--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_recheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_recheck_temp_thresholds.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -49,18 +49,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -162,15 +150,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -784,17 +763,17 @@
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="F4" s="13" t="n">
-        <v>23</v>
-      </c>
-      <c r="G4" s="13" t="n">
-        <v>9.6</v>
+      <c r="F4" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>9.1</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>17</v>
@@ -803,48 +782,52 @@
         <v>6.8</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="L4" s="3" t="n"/>
+      <c r="L4" s="3" t="n">
+        <v>16.1</v>
+      </c>
       <c r="M4" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N4" s="3" t="n"/>
+      <c r="N4" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="O4" s="3" t="n">
-        <v>84</v>
+        <v>845</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q4" s="8" t="n">
-        <v>227.8</v>
+      <c r="Q4" s="3" t="n">
+        <v>117.8</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="S4" s="8" t="n">
-        <v>651.3</v>
+      <c r="S4" s="3" t="n">
+        <v>24.5</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>54.8</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="V4" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V4" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>17.8</v>
+        <v>1.8</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>56.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>13.6</v>
@@ -863,17 +846,17 @@
         </is>
       </c>
       <c r="C5" s="3" t="n"/>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="11" t="n">
         <v>28.4</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="11" t="n">
         <v>17.6</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="G5" s="13" t="n">
-        <v>10.8</v>
+      <c r="G5" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>16.8</v>
@@ -885,52 +868,52 @@
         <v>9</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>17.6</v>
+        <v>18.4</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>19.8</v>
+        <v>15.8</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>16.9</v>
+        <v>11.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>823.5</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q5" s="8" t="n">
-        <v>28.4</v>
+        <v>3.9</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>48.4</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v>21.8</v>
+      <c r="S5" s="8" t="n">
+        <v>41.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U5" s="8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="U5" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>20.8</v>
+        <v>20</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>18.2</v>
+        <v>1.2</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -946,23 +929,23 @@
         </is>
       </c>
       <c r="C6" s="3" t="n"/>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="11" t="n">
         <v>28.6</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="11" t="n">
         <v>23.2</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="11" t="n">
         <v>10.8</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>17.6</v>
+        <v>11.6</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>7.4</v>
+        <v>0.4</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>12.6</v>
@@ -970,9 +953,11 @@
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="3" t="n"/>
+      <c r="L6" s="3" t="n">
+        <v>18.6</v>
+      </c>
       <c r="M6" s="3" t="n">
-        <v>162.4</v>
+        <v>1.8</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>18.2</v>
@@ -981,10 +966,10 @@
         <v>86</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>481.1</v>
+        <v>47.1</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>21.8</v>
@@ -996,18 +981,20 @@
         <v>56.4</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="V6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="X6" s="8" t="n">
+      <c r="X6" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="Y6" s="3" t="n"/>
+      <c r="Y6" s="3" t="n">
+        <v>57.8</v>
+      </c>
       <c r="Z6" s="3" t="n">
         <v>14</v>
       </c>
@@ -1025,64 +1012,66 @@
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="11" t="n">
         <v>30.4</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="11" t="n">
         <v>24.1</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="11" t="n">
         <v>12.6</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>8.6</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="K7" s="8" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="8" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>109.2</v>
+      <c r="K7" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54621561
+81
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P7" s="8" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="Q7" s="8" t="n">
+        <v>28341.2</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q7" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>42.6</v>
+        <v>4.6</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="W7" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="W7" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1111,37 +1100,39 @@
       <c r="D8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="8" t="n">
-        <v>17.8</v>
+      <c r="E8" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>20.9</v>
+        <v>23.9</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="I8" s="3" t="n"/>
+      <c r="I8" s="3" t="n">
+        <v>14.9</v>
+      </c>
       <c r="J8" s="3" t="n">
-        <v>19.2</v>
+        <v>1.2</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10</v>
+        <v>18.6</v>
       </c>
       <c r="L8" s="3" t="n"/>
       <c r="M8" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="N8" s="8" t="n">
+      <c r="N8" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>81.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>30.6</v>
@@ -1150,15 +1141,19 @@
         <v>21.2</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="T8" s="3" t="n"/>
-      <c r="U8" s="3" t="n"/>
+        <v>1.7</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>4.2</v>
+      </c>
       <c r="V8" s="3" t="n">
-        <v>25.8</v>
+        <v>29.8</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>19.4</v>
+        <v>1.4</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>18.7</v>
@@ -1167,7 +1162,7 @@
         <v>56.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>1194.4</v>
+        <v>14.4</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1186,36 +1181,43 @@
       <c r="D9" s="10" t="n">
         <v>145.8</v>
       </c>
-      <c r="E9" s="11" t="n"/>
+      <c r="E9" s="10" t="n">
+        <v>88.7</v>
+      </c>
       <c r="F9" s="10" t="n">
-        <v>117.1</v>
+        <v>0.7</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>63.7</v>
+        <v>63</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>134.6</v>
+        <v>34.1</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>256.4</v>
+        <v>56.4</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>10</v>
+        <v>1.1</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>1.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>0.4</v>
+        <v>83.2</v>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1717
+20 4
+89 8 6
+</t>
+        </is>
       </c>
       <c r="O9" s="3" t="n">
-        <v>18.5</v>
+        <v>84.7</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>16</v>
@@ -1224,31 +1226,31 @@
         <v>145.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>10.6</v>
+        <v>196.1</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>122.6</v>
+        <v>12.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>288.1</v>
+        <v>51</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>2938.1</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>73.5</v>
+        <v>13.4</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>970.1</v>
+        <v>914.4</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>95.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>1.4</v>
+        <v>194.5</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1264,32 +1266,32 @@
         </is>
       </c>
       <c r="C10" s="3" t="n"/>
-      <c r="D10" s="13" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E10" s="13" t="n">
+      <c r="D10" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E10" s="10" t="n">
         <v>17.7</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="10" t="n">
         <v>23.4</v>
       </c>
-      <c r="G10" s="13" t="n">
-        <v>11.5</v>
+      <c r="G10" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>16.5</v>
+        <v>46.4</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>6.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>11.3</v>
+        <v>1.3</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>18.6</v>
+        <v>21.8</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>16.6</v>
@@ -1298,10 +1300,10 @@
         <v>18</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>84.7</v>
+        <v>820.1</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>29.2</v>
@@ -1310,28 +1312,28 @@
         <v>21.2</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>20.5</v>
+        <v>0.6</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>51</v>
+        <v>4.5</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>25.4</v>
+        <v>1.4</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>19.5</v>
+        <v>1.5</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>19.9</v>
+        <v>19.1</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>11.1</v>
+        <v>8.9</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>13.4</v>
+        <v>1.4</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1348,69 +1350,73 @@
       </c>
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>16.8</v>
+        <v>6.4</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>4.6</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G11" s="3" t="n"/>
+        <v>23.1</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="H11" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="I11" s="3" t="n"/>
+      <c r="I11" s="3" t="n">
+        <v>34.1</v>
+      </c>
       <c r="J11" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>8</v>
+        <v>1.1</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>18</v>
+        <v>86.09999999999999</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>890.1</v>
+        <v>89</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>44.1</v>
+        <v>0.4</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>6.8</v>
+        <v>48.4</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>900.6</v>
-      </c>
-      <c r="S11" s="8" t="n">
-        <v>18.4</v>
+        <v>700.6</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>48.4</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>47.5</v>
+        <v>5.1</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>20.2</v>
+        <v>1.1</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>25.6</v>
+        <v>15.6</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>600.1</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>13</v>
+        <v>1.3</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1426,46 +1432,46 @@
         </is>
       </c>
       <c r="C12" s="3" t="n"/>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="11" t="n">
         <v>28.2</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F12" s="11" t="n">
         <v>23.1</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="G12" s="11" t="n">
         <v>10.2</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>16.4</v>
+        <v>1.4</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>6.2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>10</v>
+        <v>21.8</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>49.9</v>
+        <v>14.6</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>17.4</v>
+        <v>1.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>19.9</v>
+        <v>19.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>89</v>
+        <v>23.5</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q12" s="8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q12" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="R12" s="3" t="n">
@@ -1475,7 +1481,7 @@
         <v>21.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>57.1</v>
+        <v>58</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>16.2</v>
@@ -1484,13 +1490,13 @@
         <v>25.6</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>19.8</v>
+        <v>1.8</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>600.1</v>
+        <v>6</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>13</v>
@@ -1509,69 +1515,71 @@
         </is>
       </c>
       <c r="C13" s="3" t="n"/>
-      <c r="D13" s="13" t="n">
-        <v>26</v>
-      </c>
-      <c r="E13" s="13" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G13" s="13" t="n">
+      <c r="D13" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G13" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>17.4</v>
+        <v>1.4</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L13" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>19.8</v>
+      </c>
       <c r="M13" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>16.9</v>
+        <v>1.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>83.5</v>
+        <v>24.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q13" s="8" t="n">
-        <v>66</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>19.9</v>
+        <v>1.9</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>58</v>
+        <v>5.5</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>14.9</v>
+        <v>14</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="W13" s="8" t="n">
-        <v>17.4</v>
+      <c r="W13" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>10.6</v>
@@ -1590,71 +1598,71 @@
         </is>
       </c>
       <c r="C14" s="3" t="n"/>
-      <c r="D14" s="13" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E14" s="13" t="n">
+      <c r="D14" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E14" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="F14" s="13" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G14" s="13" t="n">
+      <c r="F14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>19</v>
+        <v>10.9</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M14" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M14" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>74.5</v>
+        <v>213.4</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>5.8</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>26.8</v>
+        <v>46.2</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="S14" s="8" t="n">
-        <v>118.2</v>
+      <c r="S14" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>21.5</v>
+        <v>52.1</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>17</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>23.6</v>
+        <v>50.1</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="X14" s="3" t="n">
-        <v>1.9</v>
+      <c r="X14" s="8" t="n">
+        <v>39.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>61.8</v>
+        <v>6</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1673,32 +1681,36 @@
         </is>
       </c>
       <c r="C15" s="3" t="n"/>
-      <c r="D15" s="13" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>11</v>
+      <c r="D15" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>10.2</v>
+        <v>1.6</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42292792
+64
+</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>64.59999999999999</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>18.6</v>
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>220.5</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>16.8</v>
@@ -1710,22 +1722,22 @@
         <v>84</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>13.4</v>
+        <v>72.2</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R15" s="3" t="n">
-        <v>21.2</v>
+      <c r="R15" s="8" t="n">
+        <v>12.6</v>
       </c>
       <c r="S15" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>22.1</v>
+        <v>111.9</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>25.4</v>
@@ -1737,10 +1749,10 @@
         <v>17.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>114.6</v>
+        <v>14.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1756,18 +1768,20 @@
         </is>
       </c>
       <c r="C16" s="3" t="n"/>
-      <c r="D16" s="10" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="10" t="n">
-        <v>193.9</v>
-      </c>
-      <c r="G16" s="9" t="n">
-        <v>25</v>
+      <c r="D16" s="11" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>-11</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>20.6</v>
@@ -1776,52 +1790,52 @@
         <v>50.6</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>220.3</v>
+        <v>18.6</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>84</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>72.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>138.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>102.1</v>
+        <v>132.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>28.8</v>
+        <v>988.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>211.9</v>
+        <v>53.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>814.4</v>
+        <v>813.4</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>122.8</v>
+        <v>12.8</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>94.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>933.5</v>
+        <v>93.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>55</v>
+        <v>202.5</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1837,29 +1851,33 @@
         </is>
       </c>
       <c r="C17" s="3" t="n"/>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="11" t="n">
         <v>27.8</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="11" t="n">
         <v>22.8</v>
       </c>
-      <c r="G17" s="13" t="n">
-        <v>10</v>
+      <c r="G17" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="I17" s="3" t="n">
-        <v>6.1</v>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+61
+</t>
+        </is>
       </c>
       <c r="J17" s="3" t="n">
         <v>10.1</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>18.6</v>
@@ -1867,42 +1885,44 @@
       <c r="M17" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N17" s="3" t="n"/>
+      <c r="N17" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O17" s="3" t="n">
-        <v>84</v>
+        <v>284.6</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="R17" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="R17" s="8" t="n">
         <v>20.4</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>53.2</v>
+        <v>482.1</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>17.2</v>
+        <v>1.2</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>19.7</v>
+        <v>1.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>12.9</v>
+        <v>1.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1918,74 +1938,74 @@
         </is>
       </c>
       <c r="C18" s="3" t="n"/>
-      <c r="D18" s="9" t="n">
-        <v>30.55</v>
-      </c>
-      <c r="E18" s="9" t="n">
+      <c r="D18" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G18" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>13.6</v>
-      </c>
       <c r="H18" s="3" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>1.4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>18.6</v>
+        <v>43.6</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.4</v>
+        <v>6</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>18.6</v>
+        <v>12.6</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>1.6</v>
+        <v>164.8</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>18.1</v>
+        <v>1</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>12.1</v>
+        <v>118.2</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>504.1</v>
+        <v>2.8</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>41.5</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>24.8</v>
+        <v>0.1</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>432.1</v>
+        <v>46.8</v>
       </c>
       <c r="U18" s="3" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="V18" s="3" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="W18" s="8" t="n">
         <v>6.2</v>
       </c>
-      <c r="V18" s="3" t="n">
-        <v>864.1</v>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>20.2</v>
-      </c>
       <c r="X18" s="3" t="n">
-        <v>10.1</v>
+        <v>109.1</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>580.1</v>
+        <v>8</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>9.4</v>
+        <v>19.4</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2001,72 +2021,72 @@
         </is>
       </c>
       <c r="C19" s="3" t="n"/>
-      <c r="D19" s="13" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E19" s="13" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F19" s="13" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="G19" s="13" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>17.6</v>
+      <c r="D19" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>0.4</v>
+        <v>13.5</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="N19" s="3" t="n"/>
+        <v>1.2</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="O19" s="3" t="n">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="R19" s="8" t="n">
-        <v>209.8</v>
+        <v>2.6</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>19.4</v>
+        <v>1.4</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>46.8</v>
+        <v>4.5</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>22</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>26.9</v>
+        <v>26.1</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2082,41 +2102,41 @@
         </is>
       </c>
       <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n">
-        <v>10.6</v>
+      <c r="D20" s="9" t="n">
+        <v>1.6</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>23.1</v>
+        <v>12.4</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>11.9</v>
+        <v>8.6</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>71.90000000000001</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>12.6</v>
+        <v>1.6</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N20" s="8" t="n">
-        <v>18.1</v>
+        <v>1.4</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>881</v>
+        <v>80.8</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>2.8</v>
@@ -2128,28 +2148,28 @@
         <v>21.8</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>20.9</v>
+        <v>2.9</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>148.5</v>
+        <v>56</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>26.4</v>
+        <v>465.4</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>50.5</v>
+        <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>58.8</v>
+        <v>8</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2165,62 +2185,62 @@
         </is>
       </c>
       <c r="C21" s="3" t="n"/>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q21" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="E21" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="F21" s="13" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G21" s="13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>26.5</v>
-      </c>
       <c r="R21" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>19.8</v>
+        <v>1.5</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v>15.9</v>
+        <v>68.3</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>18.6</v>
@@ -2229,7 +2249,7 @@
         <v>18</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>12.6</v>
@@ -2248,74 +2268,74 @@
         </is>
       </c>
       <c r="C22" s="3" t="n"/>
-      <c r="D22" s="13" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="E22" s="13" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="F22" s="13" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>17</v>
+      <c r="D22" s="11" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>10.8</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>17.6</v>
+        <v>1.7</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>16.6</v>
+        <v>4.1</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="K22" s="8" t="n">
-        <v>18.8</v>
+        <v>72.40000000000001</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>18.2</v>
+        <v>23</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>188</v>
+        <v>2.8</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>2.6</v>
+        <v>7.3</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>19.8</v>
+        <v>12.5</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>68.3</v>
+        <v>267.8</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v>19.6</v>
+        <v>39</v>
+      </c>
+      <c r="V22" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>16.8</v>
+        <v>25.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>17.5</v>
+        <v>1.5</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>16</v>
+        <v>726.8</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>25.4</v>
+        <v>35.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2338,67 +2358,65 @@
         <v>99.40000000000001</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>110.8</v>
-      </c>
-      <c r="G23" s="9" t="n">
-        <v>56.8</v>
+        <v>117.6</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>56.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>84.8</v>
+        <v>34.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4.2</v>
+        <v>32.3</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>52.9</v>
+        <v>5.9</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>93</v>
+        <v>1.6</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>285</v>
+        <v>185</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>18.8</v>
+        <v>357.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>126.8</v>
+        <v>0.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>7.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>740.8</v>
+        <v>740.4</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>103.9</v>
+        <v>113.4</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>111.4</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>96.7</v>
+        <v>68.3</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>975.1</v>
+        <v>175.1</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>123.5</v>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v>95.59999999999999</v>
-      </c>
+        <v>1238.5</v>
+      </c>
+      <c r="W23" s="3" t="n"/>
       <c r="X23" s="3" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>30.5</v>
+        <v>3152.1</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>52.8</v>
+        <v>62.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2414,74 +2432,74 @@
         </is>
       </c>
       <c r="C24" s="3" t="n"/>
-      <c r="D24" s="13" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E24" s="13" t="n">
+      <c r="D24" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E24" s="10" t="n">
         <v>17.9</v>
       </c>
-      <c r="F24" s="13" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G24" s="13" t="n">
-        <v>11.2</v>
+      <c r="F24" s="10" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.9</v>
+        <v>11.7</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>52.9</v>
+        <v>6.6</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>6.8</v>
+        <v>0.1</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>9.4</v>
+        <v>1.4</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>28.1</v>
+        <v>0.8</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>20.7</v>
+        <v>0.3</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>53.5</v>
+        <v>3.5</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>24.7</v>
+        <v>4.7</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>19.1</v>
+        <v>3.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>18.9</v>
+        <v>0.8</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>12.8</v>
+        <v>121.6</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2497,21 +2515,23 @@
         </is>
       </c>
       <c r="C25" s="3" t="n"/>
-      <c r="D25" s="14" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>45.6</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>18.8</v>
+      <c r="F25" s="9" t="n">
+        <v>4.8</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>26.1</v>
+        <v>16.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>6.6</v>
+        <v>1.4</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>3.2</v>
@@ -2520,46 +2540,46 @@
         <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>16.2</v>
+        <v>47.1</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>18.4</v>
+        <v>16.9</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>83.5</v>
+        <v>356.4</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>34.1</v>
+        <v>54.1</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>19.4</v>
+        <v>0.8</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>13.4</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>605.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>0.2</v>
+        <v>138.1</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>13.9</v>
+        <v>438.1</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>88.8</v>
+        <v>8.9</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>2.8</v>
@@ -2578,44 +2598,44 @@
         </is>
       </c>
       <c r="C26" s="3" t="n"/>
-      <c r="D26" s="13" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="E26" s="13" t="n">
+      <c r="D26" s="9" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="E26" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F26" s="13" t="n">
-        <v>23</v>
-      </c>
-      <c r="G26" s="13" t="n">
-        <v>11.6</v>
+      <c r="F26" s="8" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16</v>
+        <v>11.7</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>304.1</v>
+        <v>0.1</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M26" s="3" t="n">
-        <v>16.8</v>
+      <c r="M26" s="8" t="n">
+        <v>68.09999999999999</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>16.1</v>
+        <v>18.9</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>86</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>28.8</v>
@@ -2624,7 +2644,7 @@
         <v>21.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>8</v>
+        <v>20.7</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>52.2</v>
@@ -2632,20 +2652,20 @@
       <c r="U26" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="V26" s="3" t="n">
-        <v>24.4</v>
+      <c r="V26" s="8" t="n">
+        <v>4494.4</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>19.6</v>
+        <v>18.6</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>28.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>12.8</v>
+        <v>1.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2661,43 +2681,47 @@
         </is>
       </c>
       <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="3" t="n">
         <v>21.4</v>
-      </c>
-      <c r="E27" s="14" t="n"/>
-      <c r="F27" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G27" s="8" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>465.4</v>
-      </c>
-      <c r="I27" s="8" t="n">
-        <v>194.6</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="M27" s="8" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>27.4</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>20.8</v>
@@ -2708,7 +2732,7 @@
       <c r="T27" s="3" t="n">
         <v>56.7</v>
       </c>
-      <c r="U27" s="3" t="n">
+      <c r="U27" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="V27" s="3" t="n">
@@ -2718,7 +2742,7 @@
         <v>19.8</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>20.1</v>
+        <v>22.1</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>64</v>
@@ -2740,72 +2764,74 @@
         </is>
       </c>
       <c r="C28" s="3" t="n"/>
-      <c r="D28" s="13" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="E28" s="13" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="F28" s="13" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G28" s="13" t="n">
+      <c r="D28" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G28" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>16</v>
+      <c r="H28" s="8" t="n">
+        <v>60.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>24</v>
+        <v>4.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="8" t="n">
+      <c r="L28" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M28" s="8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="N28" s="8" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="O28" s="3" t="n"/>
+      <c r="M28" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="P28" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>27.4</v>
+        <v>22.4</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>20.7</v>
+        <v>0.7</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v>95.59999999999999</v>
+        <v>56.1</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>28.6</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>19.8</v>
+        <v>1.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>59</v>
+        <v>52.5</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2821,14 +2847,14 @@
         </is>
       </c>
       <c r="C29" s="3" t="n"/>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="E29" s="13" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>22.4</v>
+      <c r="E29" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>2.1</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>9.4</v>
@@ -2837,22 +2863,22 @@
         <v>16.8</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.4</v>
+        <v>424.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>19.9</v>
+        <v>12.1</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>89</v>
@@ -2870,22 +2896,22 @@
         <v>19.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>29.2</v>
+        <v>5.5</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="V29" s="8" t="n">
-        <v>229.6</v>
+      <c r="V29" s="3" t="n">
+        <v>43.6</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>19</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>19.6</v>
+        <v>12.6</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>66.2</v>
+        <v>6.2</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>9.800000000000001</v>
@@ -2905,71 +2931,73 @@
       </c>
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="10" t="n">
-        <v>133.4</v>
+        <v>1353.2</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>85.8</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>22.1</v>
+        <v>2.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>47.4</v>
+        <v>31.6</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>46.8</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>33</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>9.1</v>
+        <v>41.7</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>2.8</v>
+        <v>89</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>115.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>139</v>
+        <v>139.1</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>102</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>102.4</v>
+        <v>19.6</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>298</v>
+        <v>5.5</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="V30" s="3" t="n"/>
+        <v>28.1</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>118.2</v>
+      </c>
       <c r="W30" s="3" t="n">
-        <v>95</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>0.4</v>
+        <v>4.4</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>5.6</v>
+        <v>34.6</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>45.1</v>
+        <v>4981.1</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2985,72 +3013,72 @@
         </is>
       </c>
       <c r="C31" s="3" t="n"/>
-      <c r="D31" s="13" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E31" s="13" t="n">
+      <c r="D31" s="9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E31" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="F31" s="13" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="G31" s="13" t="n">
+      <c r="F31" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G31" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="H31" s="8" t="n">
-        <v>10.6</v>
+      <c r="H31" s="3" t="n">
+        <v>876.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="K31" s="3" t="n"/>
+      <c r="K31" s="3" t="n">
+        <v>7.1</v>
+      </c>
       <c r="L31" s="3" t="n">
-        <v>944.1</v>
+        <v>94</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>85.59999999999999</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="O31" s="3" t="n"/>
       <c r="P31" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>26.4</v>
+        <v>6.4</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>20.4</v>
+        <v>2.4</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>20.4</v>
+        <v>2.4</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>59.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>1.4</v>
+        <v>14.2</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>23.6</v>
+        <v>43.6</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>19.8</v>
+        <v>8.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>67.2</v>
+        <v>0.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3066,62 +3094,62 @@
         </is>
       </c>
       <c r="C32" s="3" t="n"/>
-      <c r="D32" s="13" t="n">
+      <c r="D32" s="11" t="n">
         <v>26.2</v>
       </c>
-      <c r="E32" s="13" t="n">
+      <c r="E32" s="11" t="n">
         <v>17.6</v>
       </c>
-      <c r="F32" s="13" t="n">
+      <c r="F32" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="G32" s="11" t="n">
         <v>8.6</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>26.7</v>
+        <v>1.6</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>1.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>482.4</v>
+        <v>1.8</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>18.4</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="P32" s="8" t="n">
-        <v>92.40000000000001</v>
+        <v>28.5</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>2.1</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>19.8</v>
+        <v>1.2</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>56.8</v>
+        <v>6.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>22.6</v>
+        <v>2.6</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>18.8</v>
@@ -3130,7 +3158,7 @@
         <v>19.5</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>71</v>
+        <v>21.8</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>8</v>
@@ -3149,29 +3177,29 @@
         </is>
       </c>
       <c r="C33" s="3" t="n"/>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="E33" s="13" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F33" s="13" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="G33" s="13" t="n">
+      <c r="E33" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G33" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>15.2</v>
+        <v>1.2</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>1</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>18.4</v>
@@ -3180,41 +3208,43 @@
         <v>565.1</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>11.8</v>
+        <v>16.1</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>84</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q33" s="8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q33" s="3" t="n">
         <v>26.6</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="U33" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="V33" s="3" t="n"/>
+      <c r="V33" s="3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="W33" s="3" t="n">
-        <v>18.6</v>
+        <v>19.6</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>75</v>
+        <v>16.6</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3230,56 +3260,56 @@
         </is>
       </c>
       <c r="C34" s="3" t="n"/>
-      <c r="D34" s="13" t="n">
+      <c r="D34" s="11" t="n">
         <v>28.2</v>
       </c>
-      <c r="E34" s="13" t="n">
+      <c r="E34" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="F34" s="13" t="n">
+      <c r="F34" s="11" t="n">
         <v>23.1</v>
       </c>
-      <c r="G34" s="13" t="n">
-        <v>10.2</v>
+      <c r="G34" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>7</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>10</v>
+        <v>10.8</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q34" s="8" t="n">
+      <c r="Q34" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>21.9</v>
+        <v>2.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>57.2</v>
+        <v>57.6</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>15.3</v>
@@ -3288,16 +3318,16 @@
         <v>24.6</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>20</v>
+        <v>18.6</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>10.2</v>
+        <v>16.2</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3313,72 +3343,74 @@
         </is>
       </c>
       <c r="C35" s="3" t="n"/>
-      <c r="D35" s="13" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E35" s="13" t="n">
+      <c r="D35" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E35" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="F35" s="13" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G35" s="13" t="n">
+      <c r="F35" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="G35" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="H35" s="8" t="n">
-        <v>17</v>
+      <c r="H35" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="8" t="n">
+      <c r="L35" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="N35" s="3" t="n"/>
+      <c r="N35" s="3" t="n">
+        <v>18.3</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>900.6</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>24.2</v>
+        <v>4.2</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v>20.4</v>
+        <v>6.2</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>2.4</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>18.8</v>
+        <v>20</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>20.8</v>
+        <v>2.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>86.5</v>
+        <v>6</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>3.2</v>
+        <v>32.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3394,61 +3426,63 @@
         </is>
       </c>
       <c r="C36" s="3" t="n"/>
-      <c r="D36" s="13" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E36" s="13" t="n">
+      <c r="D36" s="9" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="E36" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F36" s="13" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="G36" s="13" t="n">
-        <v>10.8</v>
+      <c r="F36" s="9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="N36" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L36" s="8" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="N36" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>87</v>
+        <v>83.5</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>12.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>21.8</v>
+        <v>61.8</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>22.1</v>
+        <v>2.1</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>56.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="V36" s="3" t="n"/>
+        <v>1.4</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>20.4</v>
+      </c>
       <c r="W36" s="3" t="n">
         <v>18.8</v>
       </c>
@@ -3456,10 +3490,10 @@
         <v>20.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>4.2</v>
+        <v>35.2</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3476,25 +3510,25 @@
       </c>
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="10" t="n">
-        <v>112.8</v>
-      </c>
-      <c r="E37" s="13" t="n">
+        <v>132.8</v>
+      </c>
+      <c r="E37" s="10" t="n">
         <v>88.2</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="G37" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G37" s="9" t="n">
         <v>45.6</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>5.9</v>
+        <v>20.9</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>31.2</v>
+        <v>3.1</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>18.6</v>
@@ -3503,41 +3537,43 @@
         <v>18.6</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>846.1</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>595.1</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1139.5</v>
+        <v>87</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>131.8</v>
+        <v>134.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>102.2</v>
+        <v>1922.8</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>101.7</v>
-      </c>
-      <c r="T37" s="3" t="n"/>
+        <v>7.7</v>
+      </c>
+      <c r="T37" s="3" t="n">
+        <v>56.4</v>
+      </c>
       <c r="U37" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>709.6</v>
+        <v>713.6</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>101.6</v>
+        <v>18.8</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>386.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>7.9</v>
+        <v>86.5</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>31.2</v>
@@ -3556,71 +3592,83 @@
         </is>
       </c>
       <c r="C38" s="3" t="n"/>
-      <c r="D38" s="13" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E38" s="13" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F38" s="13" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G38" s="3" t="n">
+      <c r="D38" s="10" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G38" s="8" t="n">
         <v>92.09999999999999</v>
       </c>
-      <c r="H38" s="8" t="n">
-        <v>895</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>20.9</v>
+      <c r="H38" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+9
+</t>
+        </is>
       </c>
       <c r="J38" s="3" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.7</v>
+        <v>27.3</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>16.5</v>
+        <v>1.5</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>86.09999999999999</v>
+        <v>737.8</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q38" s="3" t="n">
-        <v>26.8</v>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+248
+</t>
+        </is>
       </c>
       <c r="R38" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="S38" s="3" t="n">
-        <v>28.3</v>
+        <v>0.6</v>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+203
+</t>
+        </is>
       </c>
       <c r="T38" s="3" t="n">
-        <v>5.7</v>
+        <v>57.8</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>14.9</v>
+        <v>4.7</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>1.9</v>
+        <v>2</v>
+      </c>
+      <c r="W38" s="8" t="n">
+        <v>11.4</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>20.3</v>
+        <v>2.8</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>7.9</v>
+        <v>0.2</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>6.2</v>
@@ -3639,20 +3687,20 @@
         </is>
       </c>
       <c r="C39" s="3" t="n"/>
-      <c r="D39" s="13" t="n">
+      <c r="D39" s="11" t="n">
         <v>26.6</v>
       </c>
-      <c r="E39" s="13" t="n">
+      <c r="E39" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="F39" s="13" t="n">
+      <c r="F39" s="11" t="n">
         <v>22.6</v>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>8.800000000000001</v>
+      <c r="G39" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>4.2</v>
@@ -3661,52 +3709,52 @@
         <v>8</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>9.6</v>
+        <v>27.3</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="M39" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="R39" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="N39" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R39" s="8" t="n">
-        <v>2208.4</v>
-      </c>
       <c r="S39" s="3" t="n">
-        <v>19.8</v>
+        <v>13.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>114.9</v>
+        <v>1.9</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="V39" s="8" t="n">
-        <v>39.4</v>
+        <v>35.4</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X39" s="8" t="n">
-        <v>28.5</v>
+        <v>19.6</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>181.1</v>
+        <v>64.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>10.2</v>
+        <v>1.2</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3722,74 +3770,74 @@
         </is>
       </c>
       <c r="C40" s="3" t="n"/>
-      <c r="D40" s="13" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E40" s="13" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F40" s="13" t="n">
+      <c r="D40" s="11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F40" s="11" t="n">
         <v>22.3</v>
       </c>
-      <c r="G40" s="8" t="n">
-        <v>71.8</v>
+      <c r="G40" s="11" t="n">
+        <v>7.8</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>16.8</v>
+        <v>1.8</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>5.4</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>194.1</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N40" s="8" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N40" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="P40" s="8" t="n">
-        <v>126.2</v>
+        <v>84</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>72.59999999999999</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>20</v>
+        <v>6.6</v>
+      </c>
+      <c r="R40" s="8" t="n">
+        <v>61.6</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>56.8</v>
+        <v>5.8</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>28.8</v>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v>35.4</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>20.1</v>
+        <v>11.6</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>81.5</v>
+        <v>14.4</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3805,70 +3853,72 @@
         </is>
       </c>
       <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E41" s="8" t="n">
+      <c r="D41" s="11" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E41" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="F41" s="14" t="n"/>
+      <c r="F41" s="11" t="n">
+        <v>21.3</v>
+      </c>
       <c r="G41" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>15</v>
+        <v>8</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>59.5</v>
+        <v>1.8</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>6</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="M41" s="3" t="n">
-        <v>17.2</v>
+      <c r="M41" s="8" t="n">
+        <v>72.09999999999999</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>15.9</v>
+        <v>18.7</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>81</v>
+        <v>840.1</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>22.6</v>
+        <v>0.3</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>17.6</v>
+        <v>12.6</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>17.2</v>
+        <v>12.2</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.9</v>
+        <v>57.8</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>19.6</v>
+        <v>14.4</v>
       </c>
       <c r="V41" s="3" t="n"/>
       <c r="W41" s="3" t="n">
-        <v>16.8</v>
+        <v>18.6</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>19.6</v>
+        <v>76.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76.5</v>
+        <v>81.5</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>14.8</v>
+        <v>2.4</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3884,47 +3934,47 @@
         </is>
       </c>
       <c r="C42" s="3" t="n"/>
-      <c r="D42" s="13" t="n">
+      <c r="D42" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="E42" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="F42" s="13" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G42" s="13" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>14</v>
+      <c r="E42" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>16.4</v>
+        <v>23.5</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>13</v>
+        <v>24.2</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>28.6</v>
+        <v>0.3</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>21</v>
@@ -3933,22 +3983,26 @@
         <v>20.4</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="U42" s="8" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="V42" s="3" t="n"/>
+      <c r="V42" s="3" t="n">
+        <v>6.9</v>
+      </c>
       <c r="W42" s="3" t="n">
-        <v>20</v>
+        <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>19.6</v>
+        <v>1.6</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>114.8</v>
-      </c>
-      <c r="Z42" s="3" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>14.8</v>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -3967,69 +4021,71 @@
         <v>30.4</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G43" s="8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G43" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J43" s="8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J43" s="3" t="n">
         <v>15</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>16.4</v>
+        <v>12.4</v>
       </c>
       <c r="M43" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>13.9</v>
+        <v>1.9</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>85</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>4.9</v>
+        <v>28.6</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>0.6</v>
+        <v>30.6</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>20.6</v>
+        <v>21.8</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>18.9</v>
+        <v>2.9</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>142.6</v>
+        <v>42.6</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>26.4</v>
+        <v>6.9</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="X43" s="8" t="n">
-        <v>427</v>
+      <c r="X43" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+        <v>1.8</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>14.8</v>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4044,63 +4100,69 @@
         </is>
       </c>
       <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="E44" s="14" t="n"/>
-      <c r="F44" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="G44" s="3" t="n"/>
+      <c r="D44" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>14.2</v>
+      </c>
       <c r="H44" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="I44" s="3" t="n">
-        <v>7.6</v>
+      <c r="I44" s="8" t="n">
+        <v>125.6</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>15.3</v>
+        <v>1.3</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>18.8</v>
+        <v>11.8</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="N44" s="8" t="n">
+      <c r="N44" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="P44" s="8" t="n">
-        <v>65</v>
+        <v>80</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>765</v>
-      </c>
-      <c r="R44" s="8" t="n">
-        <v>21.8</v>
+        <v>766.1</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>157.1</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>20.9</v>
+        <v>62.6</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>147</v>
+        <v>47</v>
       </c>
       <c r="U44" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="V44" s="8" t="n">
-        <v>14.8</v>
+      <c r="V44" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="X44" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y44" s="3" t="n">
         <v>14.8</v>
       </c>
@@ -4120,74 +4182,76 @@
       </c>
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="10" t="n">
-        <v>24.8</v>
+        <v>28.6</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>17.1</v>
+        <v>1.1</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>22.5</v>
+        <v>2.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>92.2</v>
+        <v>32.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>33.5</v>
+        <v>3.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>61.9</v>
+        <v>61.3</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>499.6</v>
+        <v>139.6</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>998.4</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>52.6</v>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1141
+41 1
+</t>
+        </is>
       </c>
       <c r="P45" s="3" t="n">
-        <v>165</v>
+        <v>21.9</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>765</v>
+        <v>27.5</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>111.1</v>
+        <v>26.1</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>16.2</v>
+        <v>1.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>107.1</v>
+        <v>317.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>143.9</v>
+        <v>23.2</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>114.8</v>
+        <v>1.1</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>19.1</v>
+        <v>4</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>65.5</v>
+        <v>0.1</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="Z45" s="3" t="n">
-        <v>10.4</v>
-      </c>
+        <v>0.7</v>
+      </c>
+      <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4202,17 +4266,21 @@
         </is>
       </c>
       <c r="C46" s="3" t="n"/>
-      <c r="D46" s="13" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="E46" s="13" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F46" s="13" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G46" s="13" t="n">
-        <v>10.8</v>
+      <c r="D46" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+6
+</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>15.4</v>
@@ -4223,51 +4291,62 @@
       <c r="J46" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K46" s="3" t="n"/>
+      <c r="K46" s="3" t="n">
+        <v>9.4</v>
+      </c>
       <c r="L46" s="3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>7.8</v>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1141
+41 1
+</t>
+        </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>21.4</v>
+        <v>23.6</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>28.6</v>
+        <v>0.2</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>20.1</v>
+        <v>157.1</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>15.8</v>
+        <v>1.8</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>917.9</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V46" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2919292795
+24
+12
+</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>19.1</v>
+        <v>1.9</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>65.5</v>
+        <v>0.1</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>10.4</v>
+        <v>0.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_recheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_recheck_temp_thresholds.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -47,20 +47,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -165,9 +159,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -780,37 +771,61 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="n">
+      <c r="C4" s="3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G4" s="12" t="n">
         <v>9.6</v>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
+      <c r="H4" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="K4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
+      <c r="M4" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="O4" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="P4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="n">
+        <v>513.9</v>
+      </c>
       <c r="Q4" s="3" t="n">
-        <v>27.8</v>
+        <v>21.8</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" s="3" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
@@ -830,32 +845,56 @@
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="10" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="n">
+      <c r="D5" s="12" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G5" s="12" t="n">
         <v>10.8</v>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="K5" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>128.9</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>83</v>
+      </c>
       <c r="P5" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q5" s="3" t="inlineStr"/>
+        <v>12.7</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>28.4</v>
+      </c>
       <c r="R5" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="S5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="n">
+        <v>21.8</v>
+      </c>
       <c r="T5" s="3" t="n">
-        <v>54.8</v>
+        <v>56.8</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>16.8</v>
@@ -863,7 +902,7 @@
       <c r="V5" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -889,44 +928,62 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="10" t="inlineStr"/>
+      <c r="D6" s="9" t="n">
+        <v>0.8</v>
+      </c>
       <c r="E6" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="8" t="n">
+      <c r="F6" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n">
+        <v>7.4</v>
+      </c>
       <c r="J6" s="3" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="3" t="inlineStr"/>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
+        <v>10.4</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>28.6</v>
+      </c>
       <c r="R6" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S6" s="3" t="inlineStr"/>
+        <v>21.8</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>22.1</v>
+      </c>
       <c r="T6" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U6" s="8" t="n">
+        <v>656.4</v>
+      </c>
+      <c r="U6" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>24.6</v>
+        <v>25.8</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>20</v>
@@ -954,50 +1011,72 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="9" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
+      <c r="D7" s="12" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>12.6</v>
+      </c>
       <c r="H7" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
+        <v>15.6</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="J7" s="3" t="n">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
+      <c r="L7" s="8" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>484.1</v>
+      </c>
       <c r="N7" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O7" s="3" t="inlineStr"/>
+        <v>19.2</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>89</v>
+      </c>
       <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>18.5</v>
+      </c>
       <c r="T7" s="3" t="n">
-        <v>146.4</v>
+        <v>142.6</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V7" s="3" t="inlineStr"/>
+      <c r="V7" s="3" t="n">
+        <v>26.2</v>
+      </c>
       <c r="W7" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>27.8</v>
+        <v>81.8</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1014,47 +1093,61 @@
       </c>
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="8" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="E8" s="11" t="inlineStr"/>
+      <c r="F8" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>13.8</v>
+      </c>
       <c r="H8" s="8" t="n">
-        <v>95.40000000000001</v>
+        <v>19.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr"/>
+        <v>15.1</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>11.2</v>
+      </c>
       <c r="K8" s="3" t="n">
-        <v>0</v>
+        <v>16.1</v>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>81</v>
+      </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="R8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="n">
+        <v>21.2</v>
+      </c>
       <c r="S8" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="V8" s="3" t="inlineStr"/>
+        <v>24.2</v>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v>25.8</v>
+      </c>
       <c r="W8" s="3" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>19.3</v>
+        <v>18.7</v>
       </c>
       <c r="Y8" s="3" t="inlineStr"/>
       <c r="Z8" s="3" t="n">
@@ -1074,68 +1167,74 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="11" t="n">
-        <v>145.8</v>
-      </c>
-      <c r="E9" s="12" t="inlineStr"/>
-      <c r="F9" s="12" t="inlineStr"/>
+      <c r="D9" s="10" t="n">
+        <v>142.8</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>115.2</v>
+      </c>
       <c r="G9" s="3" t="n">
-        <v>27.1</v>
+        <v>57.1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>824.4</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>34.1</v>
+        <v>34.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>565.4</v>
+        <v>26.6</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>34.1</v>
+        <v>91.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr"/>
+        <v>82.2</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>89.8</v>
+      </c>
       <c r="O9" s="3" t="n">
-        <v>122.9</v>
+        <v>42.3</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1943.8</v>
+        <v>142.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1096</v>
+        <v>106</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>19.7</v>
+        <v>100.8</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>201.1</v>
+        <v>2099.1</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>24.2</v>
+        <v>992.6</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>12.2</v>
+        <v>12.7</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>911.4</v>
+        <v>11.4</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>18.7</v>
+        <v>19.1</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>0.4</v>
+        <v>229.9</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>14.4</v>
+        <v>615</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1151,70 +1250,74 @@
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="9" t="n">
-        <v>145.8</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>27.1</v>
+      <c r="D10" s="12" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>13.4</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>824.4</v>
+        <v>16.8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>34.1</v>
+        <v>6.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>565.4</v>
+        <v>11.3</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>18.6</v>
+        <v>0.5</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>34.1</v>
+        <v>18</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="N10" s="3" t="inlineStr"/>
+        <v>16.6</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>18</v>
+      </c>
       <c r="O10" s="3" t="n">
-        <v>122.9</v>
+        <v>84.7</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q10" s="8" t="n">
-        <v>943.8</v>
-      </c>
-      <c r="R10" s="8" t="n">
-        <v>96</v>
-      </c>
-      <c r="S10" s="8" t="n">
-        <v>102.6</v>
+        <v>7.2</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>20.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>163.1</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>29461</v>
+        <v>51</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>12.2</v>
+        <v>25.4</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>911.4</v>
-      </c>
-      <c r="X10" s="3" t="inlineStr"/>
+        <v>19.5</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y10" s="3" t="n">
-        <v>0.4</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>165</v>
+        <v>13.9</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1230,57 +1333,63 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="10" t="inlineStr"/>
-      <c r="E11" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
+      <c r="D11" s="12" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>11.6</v>
+      </c>
       <c r="H11" s="3" t="n">
-        <v>16.8</v>
+        <v>13.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>16.9</v>
+        <v>5.4</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="O11" s="3" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
+        <v>890.9</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="Q11" s="8" t="n">
-        <v>29.2</v>
+        <v>18.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr"/>
-      <c r="U11" s="3" t="n">
-        <v>19.9</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr"/>
-      <c r="W11" s="3" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="W11" s="3" t="inlineStr"/>
       <c r="X11" s="3" t="inlineStr"/>
-      <c r="Y11" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>13.9</v>
-      </c>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1294,65 +1403,75 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="10" t="inlineStr"/>
-      <c r="E12" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="8" t="n">
+      <c r="C12" s="3" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J12" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="H12" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr"/>
-      <c r="J12" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="8" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>182</v>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>18.9</v>
+        <v>19.2</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="P12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="Q12" s="3" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="S12" s="8" t="n">
-        <v>18.4</v>
+        <v>21.6</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>2941.2</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W12" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="X12" s="3" t="n">
-        <v>19.1</v>
+        <v>81.09999999999999</v>
+      </c>
+      <c r="U12" s="3" t="inlineStr"/>
+      <c r="V12" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="X12" s="8" t="n">
+        <v>97.09999999999999</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>28.9</v>
+        <v>60</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>13.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1367,59 +1486,77 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="10" t="inlineStr"/>
-      <c r="E13" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="8" t="n">
-        <v>11.6</v>
+      <c r="C13" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
+        <v>41.2</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="J13" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="8" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M13" s="8" t="n">
-        <v>182</v>
+        <v>9.6</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>18.9</v>
+        <v>16.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P13" s="3" t="inlineStr"/>
+        <v>283.5</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>41.4</v>
+      </c>
       <c r="Q13" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="R13" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="S13" s="8" t="n">
-        <v>18.4</v>
+        <v>26</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>2941.2</v>
-      </c>
-      <c r="U13" s="3" t="inlineStr"/>
+        <v>51.1</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="V13" s="8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W13" s="8" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="W13" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="X13" s="3" t="inlineStr"/>
-      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="Y13" s="3" t="n">
+        <v>60</v>
+      </c>
       <c r="Z13" s="3" t="n">
-        <v>13.8</v>
+        <v>1.3</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1435,58 +1572,74 @@
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="10" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
+      <c r="D14" s="12" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="H14" s="3" t="n">
-        <v>16.4</v>
+        <v>27.8</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>16</v>
+        <v>6.6</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>191.6</v>
+        <v>11</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr"/>
-      <c r="N14" s="3" t="n">
-        <v>19.2</v>
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>87.8</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="8" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>24.9</v>
+        <v>74.5</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q14" s="8" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>19.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>51.1</v>
+        <v>58</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>14</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="W14" s="3" t="inlineStr"/>
+        <v>22.6</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>3.4</v>
+      </c>
       <c r="X14" s="3" t="n">
-        <v>19.1</v>
+        <v>16.8</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>161</v>
+        <v>61</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>13.8</v>
+        <v>10.6</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1502,52 +1655,72 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="10" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
+      <c r="D15" s="12" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>17.6</v>
+      </c>
       <c r="I15" s="3" t="n">
-        <v>16</v>
+        <v>6.4</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
+        <v>10.2</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="N15" s="3" t="n">
-        <v>16.9</v>
+        <v>18.1</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
+        <v>84</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>28.8</v>
+      </c>
       <c r="R15" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="S15" s="3" t="inlineStr"/>
+        <v>21.2</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>20.7</v>
+      </c>
       <c r="T15" s="3" t="n">
-        <v>58</v>
+        <v>52.1</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="W15" s="3" t="inlineStr"/>
-      <c r="X15" s="3" t="inlineStr"/>
+        <v>25.4</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>19.3</v>
+      </c>
       <c r="Y15" s="3" t="n">
-        <v>161</v>
+        <v>25</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>10.6</v>
+        <v>114.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1563,46 +1736,74 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="11" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="E16" s="12" t="inlineStr"/>
-      <c r="F16" s="12" t="inlineStr"/>
-      <c r="G16" s="9" t="n">
-        <v>119.1</v>
+      <c r="D16" s="10" t="n">
+        <v>1198.8</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>1113.9</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>117.6</v>
-      </c>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="3" t="inlineStr"/>
-      <c r="L16" s="3" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>900.6</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>980.8</v>
+      </c>
       <c r="M16" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N16" s="3" t="inlineStr"/>
-      <c r="O16" s="3" t="inlineStr"/>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
+        <v>84</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>2281.2</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>104.1</v>
+      </c>
       <c r="S16" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="T16" s="3" t="inlineStr"/>
-      <c r="U16" s="3" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>266.2</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>86.2</v>
+      </c>
       <c r="V16" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="W16" s="3" t="inlineStr"/>
+        <v>152.8</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>94.5</v>
+      </c>
       <c r="X16" s="3" t="n">
-        <v>187.8</v>
+        <v>92.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>25</v>
+        <v>304.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>114.6</v>
+        <v>14.1</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1617,69 +1818,75 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="9" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>134.4</v>
+      <c r="C17" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>22.8</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>49.8</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>10.6</v>
+        <v>16.8</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>6.1</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>10.1</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="M17" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O17" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr"/>
       <c r="P17" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="Q17" s="8" t="n">
-        <v>128.2</v>
-      </c>
-      <c r="R17" s="8" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>98.8</v>
+        <v>13.8</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>266.2</v>
-      </c>
-      <c r="U17" s="3" t="inlineStr"/>
-      <c r="V17" s="8" t="n">
-        <v>22.8</v>
+        <v>52.2</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>148.1</v>
-      </c>
-      <c r="X17" s="8" t="n">
-        <v>99.3</v>
+        <v>12</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>302</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>61</v>
+        <v>12.2</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1694,54 +1901,74 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="13" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="E18" s="13" t="n">
+      <c r="C18" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E18" s="12" t="n">
         <v>17.8</v>
       </c>
-      <c r="F18" s="13" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="n">
-        <v>26.8</v>
+      <c r="F18" s="12" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>13.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="K18" s="3" t="inlineStr"/>
+        <v>7.4</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>88</v>
+      </c>
       <c r="L18" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M18" s="3" t="inlineStr"/>
-      <c r="N18" s="3" t="inlineStr"/>
-      <c r="O18" s="3" t="inlineStr"/>
-      <c r="P18" s="3" t="inlineStr"/>
+        <v>18.5</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>14.6</v>
+      </c>
       <c r="Q18" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr"/>
-      <c r="T18" s="3" t="inlineStr"/>
-      <c r="U18" s="3" t="inlineStr"/>
+        <v>20.4</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>22.2</v>
+      </c>
       <c r="V18" s="3" t="n">
-        <v>24.6</v>
+        <v>26.4</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="X18" s="3" t="inlineStr"/>
-      <c r="Y18" s="3" t="n">
-        <v>160.4</v>
-      </c>
-      <c r="Z18" s="3" t="n">
-        <v>12.2</v>
-      </c>
+        <v>20.2</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -1756,48 +1983,72 @@
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="n">
-        <v>12.5</v>
+      <c r="D19" s="12" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>11.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="K19" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="T19" s="3" t="n">
         <v>46.8</v>
       </c>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr"/>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="inlineStr"/>
-      <c r="R19" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="S19" s="3" t="inlineStr"/>
-      <c r="T19" s="3" t="n">
-        <v>2948.1</v>
-      </c>
-      <c r="U19" s="3" t="inlineStr"/>
-      <c r="V19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>26.1</v>
+      </c>
       <c r="W19" s="3" t="n">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y19" s="3" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="Y19" s="3" t="n">
+        <v>34</v>
+      </c>
       <c r="Z19" s="3" t="n">
-        <v>1149.5</v>
+        <v>19.9</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -1813,40 +2064,72 @@
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>24.4</v>
+      </c>
       <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
+      <c r="H20" s="8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>7.9</v>
+      </c>
       <c r="J20" s="3" t="n">
-        <v>17.8</v>
+        <v>12.6</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr"/>
-      <c r="N20" s="3" t="inlineStr"/>
-      <c r="O20" s="3" t="inlineStr"/>
-      <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>20.9</v>
+      </c>
       <c r="T20" s="3" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="U20" s="3" t="inlineStr"/>
-      <c r="V20" s="3" t="inlineStr"/>
-      <c r="W20" s="3" t="inlineStr"/>
+        <v>48.8</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W20" s="3" t="n">
+        <v>20.2</v>
+      </c>
       <c r="X20" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Y20" s="3" t="n">
+        <v>58</v>
+      </c>
       <c r="Z20" s="3" t="n">
-        <v>16</v>
+        <v>14.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -1862,38 +2145,72 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="8" t="n">
+      <c r="D21" s="12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="W21" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="X21" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="Y21" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z21" s="3" t="n">
         <v>12.6</v>
-      </c>
-      <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="n">
-        <v>288</v>
-      </c>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="3" t="inlineStr"/>
-      <c r="R21" s="3" t="inlineStr"/>
-      <c r="S21" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>948.5</v>
-      </c>
-      <c r="U21" s="3" t="inlineStr"/>
-      <c r="V21" s="3" t="inlineStr"/>
-      <c r="W21" s="3" t="inlineStr"/>
-      <c r="X21" s="3" t="inlineStr"/>
-      <c r="Y21" s="3" t="inlineStr"/>
-      <c r="Z21" s="3" t="n">
-        <v>114.9</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -1909,42 +2226,72 @@
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="3" t="inlineStr"/>
+      <c r="D22" s="12" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>4.2</v>
+      </c>
       <c r="J22" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" s="3" t="inlineStr"/>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr"/>
-      <c r="N22" s="3" t="inlineStr"/>
+        <v>7.4</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="O22" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="inlineStr"/>
+        <v>87</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="S22" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="T22" s="3" t="n">
-        <v>206</v>
-      </c>
-      <c r="U22" s="3" t="inlineStr"/>
+        <v>68.3</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="V22" s="3" t="n">
-        <v>24.4</v>
+        <v>19.6</v>
       </c>
       <c r="W22" s="8" t="n">
-        <v>18.6</v>
+        <v>16.8</v>
       </c>
       <c r="X22" s="3" t="inlineStr"/>
       <c r="Y22" s="3" t="n">
-        <v>39</v>
+        <v>16.8</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>12.6</v>
+        <v>5.7</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -1959,51 +2306,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="12" t="inlineStr"/>
-      <c r="E23" s="12" t="inlineStr"/>
-      <c r="F23" s="12" t="inlineStr"/>
+      <c r="C23" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>195.6</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>11.1</v>
+      </c>
       <c r="G23" s="3" t="n">
-        <v>10.8</v>
+        <v>26.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr"/>
+        <v>84.8</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>92.09999999999999</v>
+      </c>
       <c r="J23" s="3" t="n">
-        <v>1.4</v>
+        <v>52.9</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O23" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="inlineStr"/>
+        <v>926.8</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>140.4</v>
+      </c>
       <c r="R23" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="S23" s="3" t="inlineStr"/>
+        <v>103.4</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>1180.4</v>
+      </c>
       <c r="T23" s="3" t="n">
-        <v>168.3</v>
-      </c>
-      <c r="U23" s="3" t="inlineStr"/>
+        <v>267.9</v>
+      </c>
+      <c r="U23" s="3" t="n">
+        <v>91.90000000000001</v>
+      </c>
       <c r="V23" s="3" t="n">
-        <v>19.6</v>
+        <v>123.5</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>116.8</v>
-      </c>
-      <c r="X23" s="3" t="inlineStr"/>
+        <v>20.6</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>41.8</v>
+      </c>
       <c r="Y23" s="3" t="n">
-        <v>16</v>
+        <v>2216.1</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>5.4</v>
+        <v>24.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2018,71 +2391,75 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="9" t="n">
-        <v>945.6</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>26.6</v>
+      <c r="C24" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>12.1</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>17.9</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>31.1</v>
+        <v>6.6</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L24" s="8" t="n">
-        <v>20.8</v>
+        <v>10.6</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="N24" s="3" t="inlineStr"/>
-      <c r="O24" s="3" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>85.40000000000001</v>
+      </c>
       <c r="P24" s="3" t="n">
-        <v>156.1</v>
+        <v>3.1</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="R24" s="8" t="n">
-        <v>103.4</v>
-      </c>
-      <c r="S24" s="8" t="n">
-        <v>80.40000000000001</v>
+        <v>28.1</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>1267.8</v>
+        <v>53.5</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v>123.5</v>
-      </c>
-      <c r="W24" s="8" t="n">
-        <v>20.6</v>
+        <v>18.5</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="W24" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>94.8</v>
+        <v>18.9</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>302</v>
+        <v>61</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>52.8</v>
+        <v>12.6</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2097,58 +2474,70 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="H25" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>6.6</v>
+        <v>19.6</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>20.8</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="K25" s="3" t="inlineStr"/>
+        <v>3.2</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="L25" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="3" t="inlineStr"/>
+        <v>17.6</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>82.90000000000001</v>
+      </c>
       <c r="P25" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>28.1</v>
+        <v>3.4</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>221.8</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>20.7</v>
+        <v>19.4</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="T25" s="3" t="inlineStr"/>
-      <c r="U25" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="V25" s="3" t="inlineStr"/>
-      <c r="W25" s="3" t="n">
-        <v>19.1</v>
+        <v>20.9</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="U25" s="3" t="inlineStr"/>
+      <c r="V25" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="W25" s="8" t="n">
+        <v>86.40000000000001</v>
       </c>
       <c r="X25" s="3" t="inlineStr"/>
       <c r="Y25" s="3" t="inlineStr"/>
-      <c r="Z25" s="3" t="n">
-        <v>12.8</v>
-      </c>
+      <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2162,46 +2551,78 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>10.2</v>
+      </c>
       <c r="H26" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr"/>
+        <v>16.1</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="J26" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
-      <c r="L26" s="3" t="inlineStr"/>
+        <v>82.40000000000001</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>18.4</v>
+      </c>
       <c r="M26" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="N26" s="3" t="inlineStr"/>
-      <c r="O26" s="3" t="inlineStr"/>
-      <c r="P26" s="3" t="inlineStr"/>
+        <v>16.8</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="Q26" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="R26" s="3" t="inlineStr"/>
+        <v>28.8</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>21.2</v>
+      </c>
       <c r="S26" s="3" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>13.8</v>
+        <v>12.2</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="V26" s="3" t="inlineStr"/>
+        <v>18.8</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>29.4</v>
+      </c>
       <c r="W26" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="X26" s="3" t="inlineStr"/>
-      <c r="Y26" s="3" t="inlineStr"/>
-      <c r="Z26" s="3" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>112.8</v>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2215,46 +2636,70 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>16.2</v>
+      </c>
       <c r="I27" s="3" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>8.4</v>
+        <v>6.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M27" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr"/>
-      <c r="P27" s="3" t="inlineStr"/>
-      <c r="Q27" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="R27" s="3" t="inlineStr"/>
+      <c r="N27" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>188.9</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="n">
+        <v>20.8</v>
+      </c>
       <c r="S27" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>12.2</v>
+        <v>56.9</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="V27" s="3" t="inlineStr"/>
-      <c r="W27" s="3" t="inlineStr"/>
-      <c r="X27" s="3" t="inlineStr"/>
+        <v>12.8</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v>20.1</v>
+      </c>
       <c r="Y27" s="3" t="inlineStr"/>
       <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
@@ -2271,37 +2716,67 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" s="3" t="inlineStr"/>
+      <c r="D28" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F28" s="11" t="inlineStr"/>
       <c r="G28" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H28" s="3" t="inlineStr"/>
+        <v>9.4</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="I28" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr"/>
-      <c r="K28" s="3" t="inlineStr"/>
-      <c r="L28" s="3" t="inlineStr"/>
-      <c r="M28" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N28" s="3" t="inlineStr"/>
-      <c r="O28" s="3" t="inlineStr"/>
-      <c r="P28" s="3" t="inlineStr"/>
+        <v>4.6</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M28" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="N28" s="8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>5294</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>9.4</v>
+      </c>
       <c r="Q28" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="R28" s="3" t="inlineStr"/>
-      <c r="S28" s="3" t="inlineStr"/>
-      <c r="T28" s="3" t="inlineStr"/>
+        <v>21.4</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="S28" s="8" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>56.7</v>
+      </c>
       <c r="U28" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="V28" s="3" t="inlineStr"/>
-      <c r="W28" s="3" t="inlineStr"/>
-      <c r="X28" s="3" t="inlineStr"/>
+        <v>15.8</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y28" s="3" t="inlineStr"/>
       <c r="Z28" s="3" t="inlineStr"/>
       <c r="AA28" s="3" t="inlineStr">
@@ -2318,37 +2793,75 @@
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="inlineStr"/>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="3" t="inlineStr"/>
-      <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="8" t="n">
-        <v>16.6</v>
+      <c r="D29" s="12" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="O29" s="3" t="inlineStr"/>
-      <c r="P29" s="3" t="inlineStr"/>
+        <v>19.1</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="Q29" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="R29" s="3" t="inlineStr"/>
-      <c r="S29" s="3" t="inlineStr"/>
-      <c r="T29" s="3" t="inlineStr"/>
+        <v>25.6</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="T29" s="3" t="n">
+        <v>659.5</v>
+      </c>
       <c r="U29" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X29" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="V29" s="3" t="inlineStr"/>
-      <c r="W29" s="3" t="inlineStr"/>
-      <c r="X29" s="3" t="inlineStr"/>
-      <c r="Y29" s="3" t="inlineStr"/>
-      <c r="Z29" s="3" t="inlineStr"/>
+      <c r="Y29" s="3" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="Z29" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2363,52 +2876,74 @@
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="12" t="inlineStr"/>
-      <c r="E30" s="12" t="inlineStr"/>
-      <c r="F30" s="12" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="3" t="inlineStr"/>
+      <c r="D30" s="10" t="n">
+        <v>1952.4</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>1816.8</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>131</v>
+      </c>
       <c r="I30" s="3" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr"/>
+        <v>2016.1</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>2681.4</v>
+      </c>
       <c r="K30" s="3" t="n">
-        <v>0</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>18.6</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>17.4</v>
+        <v>836.5</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P30" s="3" t="inlineStr"/>
+        <v>420</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="Q30" s="3" t="n">
-        <v>125.6</v>
+        <v>132</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>19.8</v>
+        <v>1082</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="T30" s="3" t="inlineStr"/>
+        <v>102.2</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>298.9</v>
+      </c>
       <c r="U30" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="V30" s="3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>1818.2</v>
+      </c>
       <c r="W30" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="X30" s="3" t="inlineStr"/>
-      <c r="Y30" s="3" t="inlineStr"/>
+        <v>985.6</v>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>316.2</v>
+      </c>
       <c r="Z30" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>49.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2423,59 +2958,75 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="9" t="n">
-        <v>309.8</v>
-      </c>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="8" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="H31" s="8" t="n">
-        <v>810</v>
+      <c r="C31" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>26.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>6.6</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="8" t="n">
+        <v>318.3</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="N31" s="3" t="inlineStr"/>
-      <c r="O31" s="3" t="inlineStr"/>
-      <c r="P31" s="8" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="Q31" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="R31" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" s="3" t="inlineStr"/>
-      <c r="T31" s="3" t="inlineStr"/>
+        <v>16.7</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>59.8</v>
+      </c>
       <c r="U31" s="3" t="n">
-        <v>30.4</v>
+        <v>19.2</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>1.5</v>
+        <v>23.6</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="X31" s="3" t="inlineStr"/>
-      <c r="Y31" s="3" t="inlineStr"/>
+        <v>19.1</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>69.2</v>
+      </c>
       <c r="Z31" s="3" t="n">
-        <v>249.8</v>
+        <v>10</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -2490,54 +3041,76 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="G32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>5.6</v>
+      </c>
       <c r="H32" s="3" t="n">
-        <v>26.8</v>
+        <v>15.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>94</v>
+        <v>4.6</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K32" s="3" t="inlineStr"/>
-      <c r="L32" s="8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q32" s="8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="W32" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M32" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="N32" s="8" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="O32" s="3" t="inlineStr"/>
-      <c r="P32" s="3" t="inlineStr"/>
-      <c r="Q32" s="3" t="inlineStr"/>
-      <c r="R32" s="3" t="inlineStr"/>
-      <c r="S32" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="T32" s="3" t="inlineStr"/>
-      <c r="U32" s="8" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="W32" s="3" t="inlineStr"/>
-      <c r="X32" s="3" t="inlineStr"/>
-      <c r="Y32" s="3" t="inlineStr"/>
-      <c r="Z32" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="X32" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -2551,62 +3124,74 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>23.1</v>
+      </c>
       <c r="G33" s="3" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>18.2</v>
+        <v>17.2</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>16.9</v>
+        <v>2</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>18.4</v>
+        <v>17.4</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N33" s="3" t="inlineStr"/>
+        <v>15.6</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>16.7</v>
+      </c>
       <c r="O33" s="3" t="n">
-        <v>86.8</v>
+        <v>84</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>2.7</v>
+        <v>28.6</v>
       </c>
       <c r="R33" s="8" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>12.8</v>
+        <v>19.5</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>56.8</v>
+        <v>56</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>22.6</v>
+        <v>21.8</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X33" s="3" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y33" s="3" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Z33" s="3" t="inlineStr"/>
       <c r="AA33" s="3" t="inlineStr">
@@ -2623,39 +3208,69 @@
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="3" t="inlineStr"/>
+      <c r="D34" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>7</v>
+      </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>17.4</v>
+        <v>18.4</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="N34" s="3" t="inlineStr"/>
+        <v>17.2</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="O34" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="P34" s="3" t="inlineStr"/>
-      <c r="Q34" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R34" s="3" t="inlineStr"/>
-      <c r="S34" s="3" t="inlineStr"/>
-      <c r="T34" s="3" t="inlineStr"/>
-      <c r="U34" s="3" t="inlineStr"/>
-      <c r="V34" s="3" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="R34" s="8" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v>284.6</v>
+      </c>
       <c r="W34" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X34" s="3" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>20.1</v>
+      </c>
       <c r="Y34" s="3" t="inlineStr"/>
       <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -2671,41 +3286,71 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr"/>
-      <c r="I35" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>5.2</v>
+      </c>
       <c r="K35" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="8" t="n">
-        <v>17.2</v>
+        <v>0</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="N35" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="P35" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="R35" s="8" t="n">
+        <v>190.8</v>
+      </c>
+      <c r="S35" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="O35" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P35" s="3" t="inlineStr"/>
-      <c r="Q35" s="3" t="inlineStr"/>
-      <c r="R35" s="3" t="inlineStr"/>
-      <c r="S35" s="3" t="inlineStr"/>
-      <c r="T35" s="3" t="inlineStr"/>
-      <c r="U35" s="3" t="inlineStr"/>
-      <c r="V35" s="3" t="inlineStr"/>
-      <c r="W35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="W35" s="8" t="n">
+        <v>18.8</v>
+      </c>
       <c r="X35" s="3" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Y35" s="3" t="inlineStr"/>
       <c r="Z35" s="3" t="inlineStr"/>
@@ -2722,35 +3367,75 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="3" t="inlineStr"/>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="3" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr"/>
-      <c r="K36" s="3" t="inlineStr"/>
-      <c r="L36" s="3" t="inlineStr"/>
-      <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="3" t="inlineStr"/>
+      <c r="C36" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="P36" s="3" t="inlineStr"/>
-      <c r="Q36" s="3" t="inlineStr"/>
-      <c r="R36" s="3" t="inlineStr"/>
-      <c r="S36" s="3" t="inlineStr"/>
-      <c r="T36" s="3" t="inlineStr"/>
+        <v>87</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>26.4</v>
+      </c>
       <c r="U36" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="V36" s="3" t="inlineStr"/>
-      <c r="W36" s="3" t="inlineStr"/>
+        <v>460.8</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="X36" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="Y36" s="3" t="inlineStr"/>
+        <v>20.8</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>86.5</v>
+      </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -2766,41 +3451,75 @@
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="12" t="inlineStr"/>
-      <c r="E37" s="12" t="inlineStr"/>
-      <c r="F37" s="12" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr"/>
+      <c r="D37" s="10" t="n">
+        <v>1120.8</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>111</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>808</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>21816.4</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>219.8</v>
+      </c>
       <c r="K37" s="3" t="n">
-        <v>0</v>
+        <v>118.2</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
+        <v>90.5</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>1082.2</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="3" t="inlineStr"/>
-      <c r="R37" s="3" t="inlineStr"/>
-      <c r="S37" s="3" t="inlineStr"/>
+        <v>4920.8</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>132.8</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>1102.2</v>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>101.9</v>
+      </c>
       <c r="T37" s="3" t="n">
-        <v>26.4</v>
+        <v>288.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="V37" s="3" t="inlineStr"/>
-      <c r="W37" s="3" t="inlineStr"/>
+        <v>14.1</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="W37" s="3" t="n">
+        <v>19.4</v>
+      </c>
       <c r="X37" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="Y37" s="3" t="inlineStr"/>
-      <c r="Z37" s="3" t="inlineStr"/>
+        <v>10.1</v>
+      </c>
+      <c r="Y37" s="3" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>231.2</v>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2815,59 +3534,73 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="9" t="n">
-        <v>130.8</v>
-      </c>
-      <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="8" t="n">
-        <v>48.6</v>
+      <c r="D38" s="12" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>41.5</v>
+        <v>4.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="K38" s="8" t="n">
-        <v>15.4</v>
+        <v>6.9</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>95.09999999999999</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>866.1</v>
-      </c>
-      <c r="N38" s="8" t="n">
-        <v>92420.8</v>
-      </c>
-      <c r="O38" s="3" t="inlineStr"/>
+        <v>18.1</v>
+      </c>
+      <c r="M38" s="8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>86.09999999999999</v>
+      </c>
       <c r="P38" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="R38" s="8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S38" s="3" t="inlineStr"/>
-      <c r="T38" s="3" t="inlineStr"/>
-      <c r="U38" s="8" t="n">
-        <v>148.1</v>
+        <v>2.9</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>14.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W38" s="3" t="inlineStr"/>
-      <c r="X38" s="3" t="inlineStr"/>
-      <c r="Y38" s="3" t="inlineStr"/>
-      <c r="Z38" s="3" t="n">
-        <v>3931.2</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="Y38" s="3" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="Z38" s="3" t="inlineStr"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2881,55 +3614,75 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G39" s="3" t="inlineStr"/>
+      <c r="C39" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="H39" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="I39" s="8" t="n">
-        <v>42.1</v>
+        <v>46.8</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="3" t="inlineStr"/>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>19.4</v>
+      </c>
       <c r="M39" s="8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="N39" s="3" t="inlineStr"/>
-      <c r="O39" s="3" t="inlineStr"/>
+        <v>17.5</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>898.6</v>
+      </c>
       <c r="P39" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>26.8</v>
+        <v>41.8</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>26.6</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="S39" s="3" t="inlineStr"/>
+        <v>40.8</v>
+      </c>
+      <c r="S39" s="8" t="n">
+        <v>92.8</v>
+      </c>
       <c r="T39" s="3" t="n">
-        <v>57.7</v>
+        <v>86.8</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>14.9</v>
+        <v>18.8</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>22</v>
+        <v>29.4</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="X39" s="3" t="inlineStr"/>
-      <c r="Y39" s="3" t="inlineStr"/>
+        <v>10.6</v>
+      </c>
+      <c r="X39" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Y39" s="3" t="n">
+        <v>69.8</v>
+      </c>
       <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -2944,44 +3697,74 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr"/>
-      <c r="D40" s="3" t="inlineStr"/>
-      <c r="E40" s="3" t="inlineStr"/>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="3" t="inlineStr"/>
-      <c r="I40" s="3" t="inlineStr"/>
+      <c r="C40" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="J40" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="K40" s="3" t="inlineStr"/>
-      <c r="L40" s="3" t="inlineStr"/>
-      <c r="M40" s="3" t="inlineStr"/>
-      <c r="N40" s="3" t="inlineStr"/>
+        <v>15.4</v>
+      </c>
+      <c r="K40" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N40" s="8" t="n">
+        <v>18.8</v>
+      </c>
       <c r="O40" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="P40" s="3" t="inlineStr"/>
-      <c r="Q40" s="3" t="inlineStr"/>
-      <c r="R40" s="3" t="inlineStr"/>
-      <c r="S40" s="8" t="n">
-        <v>19.8</v>
+      <c r="P40" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>26</v>
+        <v>91.8</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="V40" s="3" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="V40" s="3" t="n">
+        <v>20.8</v>
+      </c>
       <c r="W40" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="X40" s="8" t="n">
-        <v>18.6</v>
+      <c r="X40" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>69.2</v>
+        <v>81.5</v>
       </c>
       <c r="Z40" s="3" t="inlineStr"/>
       <c r="AA40" s="3" t="inlineStr">
@@ -2997,42 +3780,74 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="8" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr"/>
-      <c r="K41" s="3" t="inlineStr"/>
-      <c r="L41" s="3" t="inlineStr"/>
-      <c r="M41" s="3" t="inlineStr"/>
-      <c r="N41" s="3" t="inlineStr"/>
+      <c r="C41" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N41" s="8" t="n">
+        <v>18.9</v>
+      </c>
       <c r="O41" s="3" t="n">
-        <v>840.1</v>
+        <v>81</v>
       </c>
       <c r="P41" s="3" t="inlineStr"/>
-      <c r="Q41" s="3" t="inlineStr"/>
-      <c r="R41" s="3" t="inlineStr"/>
-      <c r="S41" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="T41" s="3" t="inlineStr"/>
-      <c r="U41" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="V41" s="3" t="inlineStr"/>
+      <c r="Q41" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="W41" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X41" s="3" t="inlineStr"/>
+        <v>16.8</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>14.5</v>
+      </c>
       <c r="Y41" s="3" t="n">
-        <v>242.1</v>
-      </c>
-      <c r="Z41" s="3" t="inlineStr"/>
+        <v>76.5</v>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3046,36 +3861,74 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="3" t="inlineStr"/>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr"/>
+      <c r="C42" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="H42" s="3" t="inlineStr"/>
-      <c r="I42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="n">
+        <v>6.4</v>
+      </c>
       <c r="J42" s="8" t="n">
-        <v>191.6</v>
-      </c>
-      <c r="K42" s="3" t="inlineStr"/>
-      <c r="L42" s="3" t="inlineStr"/>
-      <c r="M42" s="3" t="inlineStr"/>
-      <c r="N42" s="3" t="inlineStr"/>
+        <v>11.6</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="O42" s="3" t="n">
-        <v>8540.1</v>
-      </c>
-      <c r="P42" s="3" t="inlineStr"/>
-      <c r="Q42" s="3" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>28.6</v>
+      </c>
       <c r="R42" s="3" t="n">
         <v>21</v>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
-      <c r="T42" s="3" t="inlineStr"/>
-      <c r="U42" s="3" t="inlineStr"/>
-      <c r="V42" s="3" t="inlineStr"/>
-      <c r="W42" s="3" t="inlineStr"/>
-      <c r="X42" s="3" t="inlineStr"/>
-      <c r="Y42" s="3" t="inlineStr"/>
-      <c r="Z42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W42" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="Y42" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>19.8</v>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -3090,39 +3943,75 @@
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
+      <c r="D43" s="12" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>18.5</v>
+      </c>
       <c r="H43" s="8" t="n">
-        <v>172.2</v>
-      </c>
-      <c r="I43" s="3" t="inlineStr"/>
+        <v>17.2</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="J43" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="K43" s="3" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>14.8</v>
+      </c>
       <c r="N43" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="O43" s="3" t="inlineStr"/>
-      <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="3" t="inlineStr"/>
+        <v>15.9</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="8" t="n">
+        <v>9.4</v>
+      </c>
       <c r="R43" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="S43" s="3" t="inlineStr"/>
-      <c r="T43" s="3" t="inlineStr"/>
-      <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="3" t="inlineStr"/>
-      <c r="W43" s="3" t="inlineStr"/>
-      <c r="X43" s="3" t="inlineStr"/>
+        <v>29.6</v>
+      </c>
+      <c r="S43" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W43" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y43" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z43" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="Z43" s="3" t="inlineStr"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -3137,36 +4026,42 @@
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="9" t="n">
-        <v>90</v>
+      <c r="D44" s="8" t="n">
+        <v>18.1</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>16.9</v>
+        <v>16.4</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>112</v>
-      </c>
-      <c r="G44" s="3" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>14.2</v>
+      </c>
       <c r="H44" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="I44" s="3" t="inlineStr"/>
-      <c r="J44" s="3" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I44" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr"/>
       <c r="K44" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="N44" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M44" s="8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="N44" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="O44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="n">
+        <v>80.8</v>
+      </c>
       <c r="P44" s="3" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>30.6</v>
@@ -3174,14 +4069,24 @@
       <c r="R44" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="S44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="n">
+        <v>20.9</v>
+      </c>
       <c r="T44" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="inlineStr"/>
-      <c r="W44" s="3" t="inlineStr"/>
-      <c r="X44" s="3" t="inlineStr"/>
+      <c r="U44" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W44" s="8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y44" s="3" t="n">
         <v>14.8</v>
       </c>
@@ -3199,52 +4104,74 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="12" t="inlineStr"/>
-      <c r="E45" s="12" t="inlineStr"/>
-      <c r="F45" s="12" t="inlineStr"/>
-      <c r="G45" s="9" t="n">
-        <v>16.2</v>
+      <c r="C45" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>288.4</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>60</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>92.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>33.5</v>
+        <v>22</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>61.8</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>9.4</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>109.6</v>
+        <v>1189.6</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="N45" s="3" t="inlineStr"/>
-      <c r="O45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="n">
+        <v>1102.7</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>17992.6</v>
+      </c>
       <c r="P45" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1656</v>
-      </c>
-      <c r="R45" s="3" t="inlineStr"/>
-      <c r="S45" s="3" t="inlineStr"/>
+        <v>1662</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="T45" s="3" t="n">
-        <v>17.9</v>
+        <v>217.9</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>107.1</v>
       </c>
-      <c r="V45" s="3" t="inlineStr"/>
-      <c r="W45" s="3" t="inlineStr"/>
-      <c r="X45" s="3" t="inlineStr"/>
+      <c r="V45" s="3" t="n">
+        <v>192.8</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>322.8</v>
+      </c>
       <c r="Y45" s="3" t="n">
-        <v>169.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
@@ -3261,21 +4188,23 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="3" t="n">
+      <c r="D46" s="12" t="n">
         <v>27.9</v>
       </c>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="8" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G46" s="3" t="n">
+      <c r="E46" s="12" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G46" s="12" t="n">
         <v>10.8</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>15.4</v>
+        <v>19.4</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>10.2</v>
@@ -3284,32 +4213,44 @@
       <c r="L46" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="M46" s="3" t="inlineStr"/>
-      <c r="N46" s="3" t="inlineStr"/>
+      <c r="M46" s="8" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>17.5</v>
+      </c>
       <c r="O46" s="3" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="n">
+        <v>27.6</v>
+      </c>
       <c r="R46" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="S46" s="3" t="inlineStr"/>
-      <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="8" t="n">
+      <c r="S46" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="U46" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="V46" s="3" t="inlineStr"/>
+      <c r="V46" s="3" t="n">
+        <v>23.8</v>
+      </c>
       <c r="W46" s="3" t="n">
         <v>19</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>69.8</v>
+        <v>19.1</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>10.7</v>
+        <v>119.4</v>
       </c>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_recheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_recheck_temp_thresholds.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -155,10 +161,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -771,9 +783,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>5.4</v>
-      </c>
+      <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="12" t="n">
         <v>27.8</v>
       </c>
@@ -787,7 +797,7 @@
         <v>9.6</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>6.8</v>
@@ -798,9 +808,11 @@
       <c r="K4" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="8" t="n">
-        <v>16.8</v>
+      <c r="L4" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>6.8</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>18.1</v>
@@ -809,16 +821,16 @@
         <v>84</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>513.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>21.8</v>
+        <v>27.8</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>28.5</v>
+        <v>20.5</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>54.8</v>
@@ -869,11 +881,11 @@
       <c r="K5" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="L5" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v>128.9</v>
+      <c r="L5" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>16.9</v>
@@ -881,9 +893,7 @@
       <c r="O5" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="P5" s="3" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
         <v>28.4</v>
       </c>
@@ -894,7 +904,7 @@
         <v>21.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>56.8</v>
+        <v>58</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>16.8</v>
@@ -902,14 +912,14 @@
       <c r="V5" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W5" s="8" t="n">
+      <c r="W5" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>56.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>13.6</v>
@@ -929,9 +939,9 @@
       </c>
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E6" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E6" s="12" t="n">
         <v>17.8</v>
       </c>
       <c r="F6" s="9" t="n">
@@ -953,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>10.4</v>
+        <v>18.4</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>16.8</v>
@@ -965,7 +975,7 @@
         <v>86</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>28.6</v>
@@ -977,7 +987,7 @@
         <v>22.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>656.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16.8</v>
@@ -1030,16 +1040,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>14.5</v>
+        <v>14.9</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>118.6</v>
+        <v>18.6</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>484.1</v>
+        <v>7.4</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>19.2</v>
@@ -1047,7 +1057,9 @@
       <c r="O7" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="P7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="Q7" s="3" t="n">
         <v>30.4</v>
       </c>
@@ -1058,25 +1070,25 @@
         <v>18.5</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>142.6</v>
+        <v>42.6</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>19</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>26.2</v>
+        <v>0.4</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>1.9</v>
+        <v>19.2</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>81.8</v>
+        <v>27.8</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>14</v>
+        <v>14.9</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1093,26 +1105,26 @@
       </c>
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E8" s="11" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="E8" s="12" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="H8" s="8" t="n">
-        <v>19.4</v>
+      <c r="H8" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>15.1</v>
+        <v>1.1</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="n">
@@ -1135,12 +1147,12 @@
         <v>19.7</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>45</v>
+        <v>45.9</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="V8" s="8" t="n">
+      <c r="V8" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="W8" s="3" t="n">
@@ -1173,20 +1185,18 @@
       <c r="E9" s="10" t="n">
         <v>88.7</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>115.2</v>
-      </c>
+      <c r="F9" s="13" t="inlineStr"/>
       <c r="G9" s="3" t="n">
-        <v>57.1</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>34.6</v>
+        <v>34</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>26.6</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>18.6</v>
@@ -1195,46 +1205,46 @@
         <v>91.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>82.2</v>
+        <v>83.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>89.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>42.3</v>
+        <v>423.5</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>142.8</v>
+        <v>192.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>106</v>
+        <v>186</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>100.8</v>
+        <v>102.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>2099.1</v>
+        <v>263.1</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>992.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>12.7</v>
+        <v>127.2</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>11.4</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>19.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>229.9</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>615</v>
+        <v>68</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1251,19 +1261,19 @@
       </c>
       <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="12" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>11.7</v>
+        <v>17.6</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>13.4</v>
+        <v>23.4</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>11.3</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>6.9</v>
@@ -1272,10 +1282,10 @@
         <v>11.3</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.5</v>
+        <v>51.1</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>16.6</v>
@@ -1287,7 +1297,7 @@
         <v>84.7</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>29.2</v>
@@ -1299,7 +1309,7 @@
         <v>20.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>19.9</v>
@@ -1314,7 +1324,7 @@
         <v>19.1</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>13.9</v>
@@ -1333,23 +1343,23 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="12" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F11" s="12" t="n">
+      <c r="D11" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="F11" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="G11" s="12" t="n">
-        <v>11.6</v>
+      <c r="G11" s="3" t="n">
+        <v>41.6</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>5.4</v>
+        <v>54.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>8.199999999999999</v>
@@ -1360,20 +1370,20 @@
       <c r="L11" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="M11" s="3" t="n">
-        <v>1.8</v>
+      <c r="M11" s="8" t="n">
+        <v>18.2</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>890.9</v>
+        <v>82</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q11" s="8" t="n">
-        <v>18.9</v>
+      <c r="Q11" s="3" t="n">
+        <v>28.9</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>20</v>
@@ -1382,7 +1392,7 @@
         <v>18.4</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>1.8</v>
+        <v>47.5</v>
       </c>
       <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr"/>
@@ -1403,9 +1413,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>51.3</v>
-      </c>
+      <c r="C12" s="3" t="inlineStr"/>
       <c r="D12" s="12" t="n">
         <v>28.2</v>
       </c>
@@ -1437,7 +1445,7 @@
         <v>17.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>19.2</v>
+        <v>1.9</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>89</v>
@@ -1446,16 +1454,16 @@
         <v>2.2</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="R12" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R12" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>31</v>
       </c>
       <c r="U12" s="3" t="inlineStr"/>
       <c r="V12" s="3" t="n">
@@ -1464,14 +1472,14 @@
       <c r="W12" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="X12" s="8" t="n">
-        <v>97.09999999999999</v>
+      <c r="X12" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>60</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>19.8</v>
+        <v>13.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1486,9 +1494,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
-        <v>3.1</v>
-      </c>
+      <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="12" t="n">
         <v>26</v>
       </c>
@@ -1502,7 +1508,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>41.2</v>
+        <v>17.4</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>6</v>
@@ -1511,22 +1517,22 @@
         <v>9.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8</v>
+        <v>1.1</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>283.5</v>
+        <v>23.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>41.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>26</v>
@@ -1535,15 +1541,15 @@
         <v>19.9</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>19.6</v>
+        <v>1.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>51.1</v>
+        <v>57.1</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V13" s="8" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="V13" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="W13" s="3" t="n">
@@ -1553,11 +1559,9 @@
         <v>19.7</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z13" s="3" t="n">
-        <v>1.3</v>
-      </c>
+        <v>764</v>
+      </c>
+      <c r="Z13" s="3" t="inlineStr"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1581,16 +1585,14 @@
       <c r="F14" s="12" t="n">
         <v>23.3</v>
       </c>
-      <c r="G14" s="12" t="n">
-        <v>8.199999999999999</v>
-      </c>
+      <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="n">
-        <v>27.8</v>
+        <v>47.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="J14" s="8" t="n">
+      <c r="J14" s="3" t="n">
         <v>11</v>
       </c>
       <c r="K14" s="3" t="n">
@@ -1602,8 +1604,8 @@
       <c r="M14" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="N14" s="8" t="n">
-        <v>87.8</v>
+      <c r="N14" s="3" t="n">
+        <v>17.3</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>74.5</v>
@@ -1611,32 +1613,32 @@
       <c r="P14" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="Q14" s="8" t="n">
-        <v>86.8</v>
+      <c r="Q14" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="S14" s="8" t="n">
+      <c r="S14" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>58</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>14</v>
+        <v>14.9</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>3.4</v>
+        <v>17.4</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>10.6</v>
@@ -1656,10 +1658,10 @@
       </c>
       <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="12" t="n">
-        <v>28.2</v>
+        <v>28.8</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>17.2</v>
+        <v>17.8</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>23.3</v>
@@ -1677,8 +1679,8 @@
         <v>10.2</v>
       </c>
       <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="8" t="n">
-        <v>18.6</v>
+      <c r="L15" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>16.8</v>
@@ -1687,10 +1689,10 @@
         <v>18.1</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>84</v>
+        <v>8.4</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>3.4</v>
+        <v>13.4</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>28.8</v>
@@ -1737,11 +1739,9 @@
       </c>
       <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="10" t="n">
-        <v>1198.8</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>90.90000000000001</v>
-      </c>
+        <v>1038.8</v>
+      </c>
+      <c r="E16" s="13" t="inlineStr"/>
       <c r="F16" s="10" t="n">
         <v>1113.9</v>
       </c>
@@ -1749,40 +1749,38 @@
         <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>22</v>
+        <v>3019.1</v>
       </c>
       <c r="I16" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="J16" s="3" t="n">
         <v>90.59999999999999</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>900.6</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>980.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>84</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>90.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>920</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>118.2</v>
-      </c>
+        <v>5.7</v>
+      </c>
+      <c r="P16" s="3" t="inlineStr"/>
       <c r="Q16" s="3" t="n">
-        <v>2281.2</v>
+        <v>838.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>104.1</v>
+        <v>102.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>266.2</v>
@@ -1791,19 +1789,19 @@
         <v>86.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>152.8</v>
+        <v>122.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>94.5</v>
+        <v>94.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>92.3</v>
+        <v>93.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>304.8</v>
+        <v>102</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>14.1</v>
+        <v>61</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1818,23 +1816,21 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="E17" s="12" t="n">
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="10" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E17" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="F17" s="10" t="n">
         <v>22.8</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>16.8</v>
+        <v>26.8</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>6.1</v>
@@ -1846,23 +1842,23 @@
       <c r="L17" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>84</v>
+        <v>8.4</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>3.4</v>
+        <v>8.4</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>27.6</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>20.9</v>
+        <v>20.4</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>13.8</v>
@@ -1871,19 +1867,19 @@
         <v>52.2</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>17.8</v>
+        <v>1.7</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>18.7</v>
+        <v>0.1</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>60.4</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>12.2</v>
@@ -1901,56 +1897,52 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D18" s="12" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E18" s="12" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H18" s="8" t="n">
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E18" s="14" t="inlineStr"/>
+      <c r="F18" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H18" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="J18" s="8" t="n">
-        <v>12.6</v>
+      <c r="J18" s="3" t="n">
+        <v>13.6</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>62.1</v>
+        <v>18.6</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="P18" s="8" t="n">
-        <v>14.6</v>
+        <v>78.8</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>21.8</v>
+        <v>30.4</v>
+      </c>
+      <c r="R18" s="8" t="n">
+        <v>29.8</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>11.1</v>
+        <v>21.1</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>48.8</v>
@@ -1959,7 +1951,7 @@
         <v>22.2</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>26.4</v>
+        <v>46.4</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>20.2</v>
@@ -1982,7 +1974,9 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D19" s="12" t="n">
         <v>29.8</v>
       </c>
@@ -1996,7 +1990,7 @@
         <v>11.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>6.8</v>
@@ -2005,23 +1999,23 @@
         <v>11.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.9</v>
+        <v>9.4</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>87</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="P19" s="3" t="inlineStr"/>
       <c r="Q19" s="3" t="n">
-        <v>29.6</v>
+        <v>23.6</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>20.8</v>
@@ -2030,13 +2024,13 @@
         <v>19.4</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>46.8</v>
+        <v>96.8</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>26.1</v>
+        <v>26.9</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>19.8</v>
@@ -2045,10 +2039,10 @@
         <v>19</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>19.9</v>
+        <v>14.5</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2064,13 +2058,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="E20" s="3" t="n">
+      <c r="D20" s="12" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E20" s="12" t="n">
         <v>18.2</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" s="12" t="n">
         <v>24.4</v>
       </c>
       <c r="G20" s="3" t="inlineStr"/>
@@ -2078,19 +2072,19 @@
         <v>17.4</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M20" s="8" t="n">
-        <v>117.4</v>
+      <c r="M20" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>19</v>
@@ -2114,7 +2108,7 @@
         <v>48.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>26.4</v>
@@ -2126,7 +2120,7 @@
         <v>20</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>58</v>
+        <v>58.8</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>14.4</v>
@@ -2145,16 +2139,16 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="12" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E21" s="12" t="n">
+      <c r="D21" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="E21" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F21" s="12" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="G21" s="12" t="n">
+      <c r="F21" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2164,19 +2158,19 @@
         <v>6.6</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>81</v>
@@ -2192,10 +2186,10 @@
         <v>19.5</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>26</v>
+        <v>256</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>15</v>
+        <v>15.9</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>24.4</v>
@@ -2203,11 +2197,11 @@
       <c r="W21" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="X21" s="8" t="n">
-        <v>18.8</v>
+      <c r="X21" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>12.6</v>
@@ -2226,14 +2220,14 @@
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="12" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="E22" s="12" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F22" s="12" t="n">
-        <v>23.5</v>
+      <c r="D22" s="3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>10.8</v>
@@ -2272,7 +2266,7 @@
         <v>19</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>19.5</v>
+        <v>1.9</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>68.3</v>
@@ -2280,15 +2274,17 @@
       <c r="U22" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="W22" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X22" s="3" t="inlineStr"/>
+      <c r="X22" s="3" t="n">
+        <v>155.1</v>
+      </c>
       <c r="Y22" s="3" t="n">
-        <v>16.8</v>
+        <v>16</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>5.7</v>
@@ -2306,77 +2302,75 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="10" t="n">
-        <v>195.6</v>
+        <v>19.6</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>11.1</v>
+        <v>117.8</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>26.2</v>
+        <v>25.2</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>84.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>529.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>52.9</v>
+        <v>22.9</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>6.8</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>22</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>88</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.1</v>
+        <v>12</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>926.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>140.4</v>
+        <v>44</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>103.4</v>
+        <v>103.9</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1180.4</v>
+        <v>100.4</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>267.9</v>
+        <v>8267.799999999999</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>123.5</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>20.6</v>
+        <v>25.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>41.8</v>
+        <v>94.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>2216.1</v>
+        <v>205.4</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>24.8</v>
+        <v>22.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2391,23 +2385,21 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="C24" s="3" t="inlineStr"/>
       <c r="D24" s="12" t="n">
-        <v>29.9</v>
+        <v>29.1</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>17.1</v>
+        <v>17.9</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>23.5</v>
       </c>
-      <c r="G24" s="8" t="n">
-        <v>12.1</v>
+      <c r="G24" s="12" t="n">
+        <v>11.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.9</v>
+        <v>17</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>6.6</v>
@@ -2415,7 +2407,9 @@
       <c r="J24" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="n">
+        <v>5.1</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>18.6</v>
       </c>
@@ -2444,7 +2438,7 @@
         <v>53.5</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>24.7</v>
@@ -2453,7 +2447,7 @@
         <v>19.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>18.9</v>
+        <v>12.9</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>61</v>
@@ -2474,66 +2468,62 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="D25" s="12" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>23</v>
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>2.3</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="I25" s="8" t="n">
-        <v>20.8</v>
+        <v>10.6</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N25" s="8" t="n">
-        <v>56.9</v>
+        <v>10.8</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q25" s="8" t="n">
-        <v>221.8</v>
-      </c>
+        <v>8.4</v>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
       <c r="R25" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>20.9</v>
+        <v>662.3</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="U25" s="3" t="inlineStr"/>
       <c r="V25" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="W25" s="8" t="n">
-        <v>86.40000000000001</v>
+        <v>19.8</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="X25" s="3" t="inlineStr"/>
       <c r="Y25" s="3" t="inlineStr"/>
@@ -2552,28 +2542,28 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D26" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D26" s="3" t="n">
         <v>27.4</v>
       </c>
-      <c r="E26" s="12" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F26" s="12" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G26" s="12" t="n">
-        <v>10.2</v>
+      <c r="E26" s="9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0.2</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>30.4</v>
@@ -2584,11 +2574,9 @@
       <c r="M26" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N26" s="3" t="n">
-        <v>48.4</v>
-      </c>
+      <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="n">
-        <v>69.8</v>
+        <v>6</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>3</v>
@@ -2606,10 +2594,10 @@
         <v>12.2</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>29.4</v>
+        <v>43.8</v>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v>49.4</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>18.6</v>
@@ -2618,10 +2606,10 @@
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>38.5</v>
+        <v>18.6</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>112.8</v>
+        <v>19.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2637,31 +2625,31 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G27" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G27" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>16.2</v>
+        <v>16.8</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>6.9</v>
+        <v>68.7</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.1</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18.4</v>
@@ -2669,16 +2657,18 @@
       <c r="M27" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="N27" s="8" t="n">
-        <v>21.8</v>
+      <c r="N27" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>188.9</v>
+        <v>22.2</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="Q27" s="3" t="n">
+        <v>4.1</v>
+      </c>
       <c r="R27" s="3" t="n">
         <v>20.8</v>
       </c>
@@ -2686,7 +2676,7 @@
         <v>20.7</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>56.9</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>12.8</v>
@@ -2716,13 +2706,15 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="E28" s="12" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F28" s="11" t="inlineStr"/>
+      <c r="D28" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>1.7</v>
+      </c>
       <c r="G28" s="3" t="n">
         <v>9.4</v>
       </c>
@@ -2741,25 +2733,25 @@
       <c r="L28" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="M28" s="8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="N28" s="8" t="n">
-        <v>17.8</v>
+      <c r="M28" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>5294</v>
+        <v>0</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>9.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>21.4</v>
+        <v>27.4</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="S28" s="8" t="n">
+      <c r="S28" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T28" s="3" t="n">
@@ -2839,13 +2831,13 @@
         <v>19.8</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>19.6</v>
+        <v>1.9</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>659.5</v>
+        <v>1.8</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>13.2</v>
+        <v>152.5</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>23.6</v>
@@ -2853,8 +2845,8 @@
       <c r="W29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="X29" s="8" t="n">
-        <v>12.8</v>
+      <c r="X29" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>66.2</v>
@@ -2875,27 +2867,29 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="D30" s="10" t="n">
-        <v>1952.4</v>
+        <v>1334.8</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>80.8</v>
+        <v>85.8</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>1816.8</v>
+        <v>109.8</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>47.4</v>
+        <v>48.4</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2016.1</v>
+        <v>20</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>2681.4</v>
+        <v>32.8</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>90.40000000000001</v>
@@ -2904,22 +2898,22 @@
         <v>91.40000000000001</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>836.5</v>
+        <v>185.4</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>19</v>
+        <v>904.6</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>420</v>
+        <v>43464.4</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>12.2</v>
+        <v>15.2</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>132</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>1082</v>
+        <v>102</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>102.2</v>
@@ -2928,22 +2922,22 @@
         <v>298.9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>10</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1818.2</v>
+        <v>118.2</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>985.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>418.1</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>316.2</v>
+        <v>3136.2</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>49.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2959,7 +2953,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="D31" s="12" t="n">
         <v>26.6</v>
@@ -2977,14 +2971,16 @@
         <v>26.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="n">
+        <v>85.2</v>
+      </c>
       <c r="L31" s="8" t="n">
-        <v>318.3</v>
+        <v>18.3</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>16.7</v>
@@ -3023,7 +3019,7 @@
         <v>19.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>69.2</v>
+        <v>475.1</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>10</v>
@@ -3041,20 +3037,16 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="C32" s="3" t="inlineStr"/>
       <c r="D32" s="9" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>18.9</v>
+        <v>0.9</v>
+      </c>
+      <c r="E32" s="14" t="inlineStr"/>
+      <c r="F32" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>15.2</v>
@@ -3078,37 +3070,37 @@
         <v>18.2</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>86.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q32" s="8" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="R32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R32" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="V32" s="8" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="V32" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>19.5</v>
+        <v>19.8</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>11</v>
+        <v>0.2</v>
       </c>
       <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
@@ -3124,14 +3116,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C33" s="3" t="inlineStr"/>
       <c r="D33" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>18</v>
+        <v>8.6</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>1.8</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>23.1</v>
@@ -3143,10 +3133,10 @@
         <v>17.2</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>0</v>
@@ -3155,21 +3145,21 @@
         <v>17.4</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>15.6</v>
+        <v>1.5</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>16.7</v>
+        <v>16.1</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>84</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="R33" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="R33" s="3" t="n">
         <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3184,7 +3174,7 @@
       <c r="V33" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3209,15 +3199,15 @@
       </c>
       <c r="C34" s="3" t="inlineStr"/>
       <c r="D34" s="3" t="n">
-        <v>24.2</v>
+        <v>10.8</v>
       </c>
       <c r="E34" s="9" t="n">
         <v>1.7</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="G34" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="G34" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3242,15 +3232,15 @@
         <v>18.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q34" s="8" t="n">
+      <c r="Q34" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="R34" s="8" t="n">
+      <c r="R34" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3262,14 +3252,14 @@
       <c r="U34" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="V34" s="8" t="n">
-        <v>284.6</v>
+      <c r="V34" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>20</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>20.1</v>
+        <v>20.7</v>
       </c>
       <c r="Y34" s="3" t="inlineStr"/>
       <c r="Z34" s="3" t="inlineStr"/>
@@ -3287,7 +3277,7 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="D35" s="12" t="n">
         <v>28.6</v>
@@ -3304,8 +3294,8 @@
       <c r="H35" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="I35" s="8" t="n">
-        <v>11</v>
+      <c r="I35" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>5.2</v>
@@ -3323,16 +3313,16 @@
         <v>16.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="P35" s="8" t="n">
-        <v>12.9</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="R35" s="8" t="n">
-        <v>190.8</v>
+        <v>19</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>18.9</v>
@@ -3346,7 +3336,7 @@
       <c r="V35" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="W35" s="8" t="n">
+      <c r="W35" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3367,26 +3357,24 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D36" s="9" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G36" s="3" t="n">
+      <c r="C36" s="3" t="inlineStr"/>
+      <c r="D36" s="12" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G36" s="12" t="n">
         <v>10.8</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>8</v>
@@ -3398,7 +3386,7 @@
         <v>18.6</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>17.2</v>
+        <v>7.2</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>18.8</v>
@@ -3422,7 +3410,7 @@
         <v>26.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>460.8</v>
+        <v>17</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.4</v>
@@ -3452,73 +3440,73 @@
       </c>
       <c r="C37" s="3" t="inlineStr"/>
       <c r="D37" s="10" t="n">
-        <v>1120.8</v>
+        <v>1138.8</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>80.2</v>
+        <v>88.2</v>
       </c>
       <c r="F37" s="10" t="n">
         <v>111</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>99.59999999999999</v>
+      <c r="G37" s="9" t="n">
+        <v>49.9</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>808</v>
+        <v>898</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>21816.4</v>
+        <v>210.9</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>219.8</v>
+        <v>31.8</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>118.2</v>
+        <v>1.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>90.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>11.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>1082.2</v>
+        <v>82.2</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>4920.8</v>
+        <v>12.6</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>14.9</v>
+        <v>44.5</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>132.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>1102.2</v>
+        <v>102.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>101.9</v>
+        <v>10.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>288.6</v>
+        <v>208.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>14.1</v>
+        <v>44.7</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>109.8</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>19.4</v>
+        <v>18.4</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>10.1</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>106.8</v>
+        <v>156</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>231.2</v>
+        <v>31.2</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3553,15 +3541,15 @@
         <v>4.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3580,16 +3568,16 @@
         <v>20.4</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>28.3</v>
+        <v>88.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>38.7</v>
+        <v>57.7</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>22</v>
+        <v>240.1</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>19</v>
@@ -3614,74 +3602,70 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F39" s="9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>8.800000000000001</v>
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>8</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>46.8</v>
+        <v>4.8</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>36.1</v>
+        <v>3.8</v>
       </c>
       <c r="L39" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="M39" s="8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="N39" s="8" t="n">
-        <v>19</v>
+      <c r="M39" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>898.6</v>
+        <v>8.4</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="Q39" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Q39" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="3" t="n">
-        <v>40.8</v>
-      </c>
+      <c r="R39" s="3" t="inlineStr"/>
       <c r="S39" s="8" t="n">
-        <v>92.8</v>
+        <v>19.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>86.8</v>
+        <v>26</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>18.8</v>
+        <v>15.8</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>29.4</v>
+        <v>23.9</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>10.6</v>
+        <v>18.6</v>
       </c>
       <c r="X39" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>69.8</v>
+        <v>64.2</v>
       </c>
       <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
@@ -3698,31 +3682,29 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D40" s="12" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E40" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="E40" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="F40" s="12" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>16.4</v>
+      <c r="F40" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>8.4</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J40" s="3" t="n">
-        <v>15.4</v>
-      </c>
+      <c r="J40" s="3" t="inlineStr"/>
       <c r="K40" s="8" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>19.2</v>
@@ -3737,19 +3719,19 @@
         <v>84</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>26.2</v>
+        <v>16.2</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>20.8</v>
+        <v>20</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>91.8</v>
+        <v>51.8</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>14.4</v>
@@ -3781,40 +3763,40 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>3.5</v>
+        <v>0.1</v>
       </c>
       <c r="D41" s="12" t="n">
         <v>25.4</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>17.4</v>
+        <v>17</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>3.5</v>
+        <v>43.5</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>6</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N41" s="8" t="n">
-        <v>18.9</v>
+        <v>1.7</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>81</v>
@@ -3826,12 +3808,14 @@
       <c r="R41" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="S41" s="3" t="inlineStr"/>
+      <c r="S41" s="3" t="n">
+        <v>17.2</v>
+      </c>
       <c r="T41" s="3" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v>108.4</v>
+        <v>62.5</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>10.9</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>19.6</v>
@@ -3840,7 +3824,7 @@
         <v>16.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>76.5</v>
@@ -3861,9 +3845,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="C42" s="3" t="inlineStr"/>
       <c r="D42" s="3" t="n">
         <v>30.4</v>
       </c>
@@ -3871,18 +3853,18 @@
         <v>16</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="H42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="n">
+        <v>14</v>
+      </c>
       <c r="I42" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="J42" s="8" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="J42" s="3" t="inlineStr"/>
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
@@ -3893,7 +3875,7 @@
         <v>15.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>12</v>
+        <v>17.8</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>85</v>
@@ -3905,7 +3887,7 @@
         <v>28.6</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>21</v>
+        <v>4.1</v>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
       <c r="T42" s="3" t="n">
@@ -3917,17 +3899,17 @@
       <c r="V42" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W42" s="8" t="n">
+      <c r="W42" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="X42" s="8" t="n">
+      <c r="X42" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>57</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3943,23 +3925,21 @@
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="12" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E43" s="12" t="n">
+      <c r="D43" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F43" s="12" t="n">
-        <v>22.8</v>
-      </c>
+      <c r="F43" s="14" t="inlineStr"/>
       <c r="G43" s="8" t="n">
         <v>18.5</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>17.2</v>
+        <v>19.2</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>15</v>
@@ -3982,25 +3962,25 @@
       <c r="P43" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q43" s="8" t="n">
-        <v>9.4</v>
+      <c r="Q43" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="R43" s="3" t="n">
         <v>29.6</v>
       </c>
-      <c r="S43" s="8" t="n">
-        <v>18</v>
+      <c r="S43" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v>29.9</v>
+        <v>92.59999999999999</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W43" s="8" t="n">
+      <c r="W43" s="3" t="n">
         <v>20</v>
       </c>
       <c r="X43" s="3" t="n">
@@ -4025,15 +4005,17 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="8" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="E44" s="3" t="n">
+      <c r="C44" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="E44" s="8" t="n">
         <v>16.4</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>30</v>
+        <v>21.7</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>14.2</v>
@@ -4042,17 +4024,19 @@
         <v>15.8</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr"/>
+        <v>7.6</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="K44" s="3" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M44" s="8" t="n">
-        <v>26.5</v>
+      <c r="M44" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="N44" s="8" t="n">
         <v>16.4</v>
@@ -4061,7 +4045,7 @@
         <v>80.8</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>30.6</v>
@@ -4075,14 +4059,12 @@
       <c r="T44" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="U44" s="8" t="n">
-        <v>23.6</v>
-      </c>
+      <c r="U44" s="3" t="inlineStr"/>
       <c r="V44" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W44" s="8" t="n">
-        <v>20.8</v>
+      <c r="W44" s="3" t="n">
+        <v>30</v>
       </c>
       <c r="X44" s="3" t="n">
         <v>19.6</v>
@@ -4104,56 +4086,52 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v>5.1</v>
-      </c>
+      <c r="C45" s="3" t="inlineStr"/>
       <c r="D45" s="10" t="n">
-        <v>6.6</v>
+        <v>1.8</v>
       </c>
       <c r="E45" s="10" t="n">
         <v>22.1</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>288.4</v>
+        <v>830.6</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>92.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>22</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>61.8</v>
+        <v>61</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>1189.6</v>
+        <v>1089.6</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1102.7</v>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v>17992.6</v>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="O45" s="3" t="inlineStr"/>
       <c r="P45" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1662</v>
+        <v>650.2</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>121</v>
+        <v>1.3</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>11.6</v>
+        <v>746.4</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>217.9</v>
@@ -4162,13 +4140,13 @@
         <v>107.1</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>192.8</v>
+        <v>12.8</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>112</v>
+        <v>114.8</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>322.8</v>
+        <v>1.8</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>64.40000000000001</v>
@@ -4188,23 +4166,23 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="12" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="E46" s="12" t="n">
+      <c r="D46" s="9" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="E46" s="10" t="n">
         <v>17.1</v>
       </c>
-      <c r="F46" s="12" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G46" s="12" t="n">
+      <c r="F46" s="10" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G46" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>19.4</v>
+        <v>15.4</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>10.2</v>
@@ -4213,11 +4191,11 @@
       <c r="L46" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="M46" s="8" t="n">
-        <v>85.40000000000001</v>
+      <c r="M46" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>83.09999999999999</v>
@@ -4226,19 +4204,19 @@
         <v>3.6</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>23</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>18.8</v>
+        <v>17.8</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>23.8</v>
@@ -4250,7 +4228,7 @@
         <v>19.1</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>119.4</v>
+        <v>165.4</v>
       </c>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_recheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_recheck_temp_thresholds.xlsx
@@ -808,7 +808,7 @@
       <c r="K4" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="9" t="n">
         <v>1.8</v>
       </c>
       <c r="M4" s="3" t="n">
@@ -823,10 +823,10 @@
       <c r="P4" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="12" t="n">
         <v>27.8</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="12" t="n">
         <v>20.8</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -838,8 +838,8 @@
       <c r="U4" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="V4" s="3" t="inlineStr"/>
-      <c r="W4" s="3" t="inlineStr"/>
+      <c r="V4" s="14" t="inlineStr"/>
+      <c r="W4" s="12" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
@@ -894,10 +894,10 @@
         <v>83</v>
       </c>
       <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="12" t="n">
         <v>28.4</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="12" t="n">
         <v>21.6</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -912,7 +912,7 @@
       <c r="V5" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="12" t="n">
         <v>18.6</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -977,10 +977,10 @@
       <c r="P6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="12" t="n">
         <v>28.6</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="12" t="n">
         <v>21.8</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -995,7 +995,7 @@
       <c r="V6" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="12" t="n">
         <v>20</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1060,10 +1060,10 @@
       <c r="P7" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="Q7" s="12" t="n">
         <v>30.4</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="12" t="n">
         <v>20.6</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1075,10 +1075,10 @@
       <c r="U7" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="12" t="n">
         <v>19.6</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1126,7 +1126,7 @@
       <c r="K8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="3" t="inlineStr"/>
+      <c r="L8" s="14" t="inlineStr"/>
       <c r="M8" s="3" t="n">
         <v>16.4</v>
       </c>
@@ -1137,10 +1137,10 @@
         <v>81</v>
       </c>
       <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="12" t="n">
         <v>30.6</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="12" t="n">
         <v>21.2</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1155,7 +1155,7 @@
       <c r="V8" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="12" t="n">
         <v>19.4</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1198,13 +1198,13 @@
       <c r="J9" s="3" t="n">
         <v>86.40000000000001</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="10" t="n">
         <v>91.7</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="10" t="n">
         <v>83.2</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1216,10 +1216,10 @@
       <c r="P9" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="10" t="n">
         <v>192.8</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="10" t="n">
         <v>186</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1231,10 +1231,10 @@
       <c r="U9" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="10" t="n">
         <v>127.2</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="10" t="n">
         <v>97.40000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1284,10 +1284,10 @@
       <c r="K10" s="3" t="n">
         <v>51.1</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="10" t="n">
         <v>16.6</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1299,10 +1299,10 @@
       <c r="P10" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="12" t="n">
         <v>29.2</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="12" t="n">
         <v>21.2</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1314,10 +1314,10 @@
       <c r="U10" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="10" t="n">
         <v>25.4</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="12" t="n">
         <v>19.5</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1385,7 +1385,7 @@
       <c r="Q11" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R11" s="3" t="n">
+      <c r="R11" s="12" t="n">
         <v>20</v>
       </c>
       <c r="S11" s="3" t="n">
@@ -1395,8 +1395,8 @@
         <v>47.5</v>
       </c>
       <c r="U11" s="3" t="inlineStr"/>
-      <c r="V11" s="3" t="inlineStr"/>
-      <c r="W11" s="3" t="inlineStr"/>
+      <c r="V11" s="12" t="inlineStr"/>
+      <c r="W11" s="12" t="inlineStr"/>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr"/>
       <c r="Z11" s="3" t="inlineStr"/>
@@ -1453,10 +1453,10 @@
       <c r="P12" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" s="12" t="n">
         <v>21.6</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1466,10 +1466,10 @@
         <v>31</v>
       </c>
       <c r="U12" s="3" t="inlineStr"/>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="12" t="n">
         <v>25.6</v>
       </c>
-      <c r="W12" s="8" t="n">
+      <c r="W12" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="X12" s="3" t="n">
@@ -1537,7 +1537,7 @@
       <c r="Q13" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="12" t="n">
         <v>19.9</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1549,10 +1549,10 @@
       <c r="U13" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" s="12" t="n">
         <v>25.6</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="X13" s="3" t="n">
@@ -1616,7 +1616,7 @@
       <c r="Q14" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="R14" s="3" t="n">
+      <c r="R14" s="12" t="n">
         <v>19.9</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1628,10 +1628,10 @@
       <c r="U14" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" s="12" t="n">
         <v>22.6</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="X14" s="3" t="n">
@@ -1678,7 +1678,7 @@
       <c r="J15" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K15" s="3" t="inlineStr"/>
+      <c r="K15" s="14" t="inlineStr"/>
       <c r="L15" s="3" t="n">
         <v>11.8</v>
       </c>
@@ -1697,7 +1697,7 @@
       <c r="Q15" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R15" s="3" t="n">
+      <c r="R15" s="12" t="n">
         <v>21.2</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1709,10 +1709,10 @@
       <c r="U15" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="12" t="n">
         <v>25.4</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="12" t="n">
         <v>18.8</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1757,13 +1757,13 @@
       <c r="J16" s="3" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="10" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="10" t="n">
         <v>84</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1773,10 +1773,10 @@
         <v>5.7</v>
       </c>
       <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="10" t="n">
         <v>838.2</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="10" t="n">
         <v>102.1</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1788,10 +1788,10 @@
       <c r="U16" s="3" t="n">
         <v>86.2</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="10" t="n">
         <v>122.8</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="10" t="n">
         <v>94.8</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1839,10 +1839,10 @@
         <v>10.1</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1854,10 +1854,10 @@
       <c r="P17" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="10" t="n">
         <v>27.6</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" s="12" t="n">
         <v>20.4</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1869,10 +1869,10 @@
       <c r="U17" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="12" t="n">
         <v>24.6</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="12" t="n">
         <v>19</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1923,7 +1923,7 @@
       <c r="L18" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="12" t="n">
         <v>16.2</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -1950,10 +1950,10 @@
       <c r="U18" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="9" t="n">
         <v>46.4</v>
       </c>
-      <c r="W18" s="3" t="n">
+      <c r="W18" s="12" t="n">
         <v>20.2</v>
       </c>
       <c r="X18" s="3" t="n">
@@ -2004,7 +2004,7 @@
       <c r="L19" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="12" t="n">
         <v>17.2</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2032,7 +2032,7 @@
       <c r="V19" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="W19" s="3" t="n">
+      <c r="W19" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2083,7 +2083,7 @@
       <c r="L20" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="N20" s="3" t="n">
@@ -2113,7 +2113,7 @@
       <c r="V20" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W20" s="3" t="n">
+      <c r="W20" s="12" t="n">
         <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2163,10 +2163,10 @@
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2178,7 +2178,7 @@
       <c r="P21" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="Q21" s="14" t="inlineStr"/>
       <c r="R21" s="3" t="n">
         <v>20</v>
       </c>
@@ -2194,7 +2194,7 @@
       <c r="V21" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="W21" s="8" t="n">
+      <c r="W21" s="12" t="n">
         <v>18.6</v>
       </c>
       <c r="X21" s="3" t="n">
@@ -2247,7 +2247,7 @@
       <c r="L22" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="N22" s="3" t="n">
@@ -2277,7 +2277,7 @@
       <c r="V22" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="W22" s="8" t="n">
+      <c r="W22" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2324,13 +2324,13 @@
       <c r="J23" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="10" t="n">
         <v>6.8</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="10" t="n">
         <v>88</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2342,10 +2342,10 @@
       <c r="P23" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="10" t="n">
         <v>103.9</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2357,10 +2357,10 @@
       <c r="U23" s="3" t="n">
         <v>97.59999999999999</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="10" t="n">
         <v>123.5</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="10" t="n">
         <v>25.6</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2410,10 +2410,10 @@
       <c r="K24" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="12" t="n">
         <v>17</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2425,10 +2425,10 @@
       <c r="P24" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="10" t="n">
         <v>28.1</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="10" t="n">
         <v>20.7</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2440,10 +2440,10 @@
       <c r="U24" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="10" t="n">
         <v>24.7</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="12" t="n">
         <v>19.1</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2508,8 +2508,8 @@
       <c r="P25" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="Q25" s="3" t="inlineStr"/>
-      <c r="R25" s="3" t="n">
+      <c r="Q25" s="14" t="inlineStr"/>
+      <c r="R25" s="12" t="n">
         <v>19.4</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2522,7 +2522,7 @@
       <c r="V25" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="W25" s="12" t="n">
         <v>18.4</v>
       </c>
       <c r="X25" s="3" t="inlineStr"/>
@@ -2584,7 +2584,7 @@
       <c r="Q26" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="12" t="n">
         <v>21.2</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2596,10 +2596,10 @@
       <c r="U26" s="3" t="n">
         <v>43.8</v>
       </c>
-      <c r="V26" s="8" t="n">
+      <c r="V26" s="9" t="n">
         <v>49.4</v>
       </c>
-      <c r="W26" s="3" t="n">
+      <c r="W26" s="12" t="n">
         <v>18.6</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2666,10 +2666,10 @@
       <c r="P27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="12" t="n">
         <v>20.8</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2684,7 +2684,7 @@
       <c r="V27" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W27" s="3" t="n">
+      <c r="W27" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2748,7 +2748,7 @@
       <c r="Q28" s="3" t="n">
         <v>27.4</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="R28" s="12" t="n">
         <v>20.8</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2763,7 +2763,7 @@
       <c r="V28" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="W28" s="3" t="n">
+      <c r="W28" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2827,7 +2827,7 @@
       <c r="Q29" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2842,7 +2842,7 @@
       <c r="V29" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="W29" s="3" t="n">
+      <c r="W29" s="12" t="n">
         <v>19</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2891,13 +2891,13 @@
       <c r="J30" s="3" t="n">
         <v>32.8</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="10" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="10" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="10" t="n">
         <v>185.4</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -2909,10 +2909,10 @@
       <c r="P30" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="10" t="n">
         <v>132</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="12" t="n">
         <v>102</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -2924,10 +2924,10 @@
       <c r="U30" s="3" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="10" t="n">
         <v>118.2</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="10" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -2979,10 +2979,10 @@
       <c r="K31" s="3" t="n">
         <v>85.2</v>
       </c>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="10" t="n">
         <v>18.3</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="10" t="n">
         <v>16.7</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -2994,10 +2994,10 @@
       <c r="P31" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="10" t="n">
         <v>26.4</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="12" t="n">
         <v>20.4</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3009,10 +3009,10 @@
       <c r="U31" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="V31" s="10" t="n">
         <v>23.6</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="12" t="n">
         <v>19.1</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3060,7 +3060,7 @@
       <c r="K32" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="L32" s="12" t="n">
         <v>18.4</v>
       </c>
       <c r="M32" s="3" t="n">
@@ -3078,7 +3078,7 @@
       <c r="Q32" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3090,10 +3090,10 @@
       <c r="U32" s="8" t="n">
         <v>94.59999999999999</v>
       </c>
-      <c r="V32" s="3" t="n">
+      <c r="V32" s="12" t="n">
         <v>22.6</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="12" t="n">
         <v>18.8</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3141,10 +3141,10 @@
       <c r="K33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="12" t="n">
         <v>17.4</v>
       </c>
-      <c r="M33" s="3" t="n">
+      <c r="M33" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="N33" s="3" t="n">
@@ -3159,7 +3159,7 @@
       <c r="Q33" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="12" t="n">
         <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3171,10 +3171,10 @@
       <c r="U33" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="V33" s="3" t="n">
+      <c r="V33" s="12" t="n">
         <v>21.8</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="12" t="n">
         <v>18.6</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3222,7 +3222,7 @@
       <c r="K34" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L34" s="8" t="n">
+      <c r="L34" s="12" t="n">
         <v>18.4</v>
       </c>
       <c r="M34" s="3" t="n">
@@ -3240,7 +3240,7 @@
       <c r="Q34" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="12" t="n">
         <v>21.6</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3252,10 +3252,10 @@
       <c r="U34" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="V34" s="12" t="n">
         <v>24.6</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="12" t="n">
         <v>20</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3303,7 +3303,7 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="12" t="n">
         <v>17.6</v>
       </c>
       <c r="M35" s="3" t="n">
@@ -3318,10 +3318,10 @@
       <c r="P35" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q35" s="3" t="n">
+      <c r="Q35" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="R35" s="8" t="n">
+      <c r="R35" s="12" t="n">
         <v>19</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3333,10 +3333,10 @@
       <c r="U35" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="V35" s="12" t="n">
         <v>20.4</v>
       </c>
-      <c r="W35" s="3" t="n">
+      <c r="W35" s="12" t="n">
         <v>18.8</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3382,7 +3382,7 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="12" t="n">
         <v>18.6</v>
       </c>
       <c r="M36" s="3" t="n">
@@ -3400,7 +3400,7 @@
       <c r="Q36" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="12" t="n">
         <v>21.8</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3412,10 +3412,10 @@
       <c r="U36" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="V36" s="12" t="n">
         <v>20.4</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="12" t="n">
         <v>18.8</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3460,13 +3460,13 @@
       <c r="J37" s="3" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="10" t="n">
         <v>1.6</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="12" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="10" t="n">
         <v>82.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3478,10 +3478,10 @@
       <c r="P37" s="3" t="n">
         <v>44.5</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="10" t="n">
         <v>132.8</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="12" t="n">
         <v>102.2</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3493,10 +3493,10 @@
       <c r="U37" s="3" t="n">
         <v>44.7</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="12" t="n">
         <v>109.8</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="10" t="n">
         <v>18.4</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3546,10 +3546,10 @@
       <c r="K38" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="12" t="n">
         <v>18.1</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="10" t="n">
         <v>16.5</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3561,10 +3561,10 @@
       <c r="P38" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" s="10" t="n">
         <v>26.8</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="12" t="n">
         <v>20.4</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3576,10 +3576,10 @@
       <c r="U38" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="10" t="n">
         <v>240.1</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="12" t="n">
         <v>19</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3627,7 +3627,7 @@
       <c r="K39" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="L39" s="8" t="n">
+      <c r="L39" s="12" t="n">
         <v>19.4</v>
       </c>
       <c r="M39" s="3" t="n">
@@ -3645,7 +3645,7 @@
       <c r="Q39" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="3" t="inlineStr"/>
+      <c r="R39" s="14" t="inlineStr"/>
       <c r="S39" s="8" t="n">
         <v>19.8</v>
       </c>
@@ -3655,7 +3655,7 @@
       <c r="U39" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="12" t="n">
         <v>23.9</v>
       </c>
       <c r="W39" s="3" t="n">
@@ -3706,7 +3706,7 @@
       <c r="K40" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L40" s="12" t="n">
         <v>19.2</v>
       </c>
       <c r="M40" s="3" t="n">
@@ -3736,7 +3736,7 @@
       <c r="U40" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="12" t="n">
         <v>20.8</v>
       </c>
       <c r="W40" s="3" t="n">
@@ -3789,10 +3789,10 @@
       <c r="K41" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="12" t="n">
         <v>19.4</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="9" t="n">
         <v>1.7</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3817,7 +3817,7 @@
       <c r="U41" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="12" t="n">
         <v>19.6</v>
       </c>
       <c r="W41" s="3" t="n">
@@ -3868,7 +3868,7 @@
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="L42" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="M42" s="3" t="n">
@@ -3886,7 +3886,7 @@
       <c r="Q42" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="9" t="n">
         <v>4.1</v>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
@@ -3896,7 +3896,7 @@
       <c r="U42" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" s="12" t="n">
         <v>26.4</v>
       </c>
       <c r="W42" s="3" t="n">
@@ -3947,7 +3947,7 @@
       <c r="K43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="L43" s="12" t="n">
         <v>16.4</v>
       </c>
       <c r="M43" s="3" t="n">
@@ -3977,7 +3977,7 @@
       <c r="U43" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="V43" s="3" t="n">
+      <c r="V43" s="12" t="n">
         <v>26.4</v>
       </c>
       <c r="W43" s="3" t="n">
@@ -4032,7 +4032,7 @@
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="3" t="n">
+      <c r="L44" s="12" t="n">
         <v>18.8</v>
       </c>
       <c r="M44" s="3" t="n">
@@ -4060,7 +4060,7 @@
         <v>47</v>
       </c>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="n">
+      <c r="V44" s="12" t="n">
         <v>26.4</v>
       </c>
       <c r="W44" s="3" t="n">
@@ -4108,13 +4108,13 @@
       <c r="J45" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="10" t="n">
         <v>9.9</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="10" t="n">
         <v>1089.6</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" s="10" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4124,10 +4124,10 @@
       <c r="P45" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="10" t="n">
         <v>650.2</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="10" t="n">
         <v>1.3</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4139,10 +4139,10 @@
       <c r="U45" s="3" t="n">
         <v>107.1</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="10" t="n">
         <v>12.8</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="10" t="n">
         <v>114.8</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4188,10 +4188,10 @@
         <v>10.2</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="n">
+      <c r="L46" s="12" t="n">
         <v>18.3</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="10" t="n">
         <v>16.4</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4203,10 +4203,10 @@
       <c r="P46" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="R46" s="3" t="n">
+      <c r="R46" s="10" t="n">
         <v>20.1</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4218,10 +4218,10 @@
       <c r="U46" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="12" t="n">
         <v>23.8</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="10" t="n">
         <v>19</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_recheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_recheck_temp_thresholds.xlsx
@@ -53,8 +53,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
@@ -65,8 +65,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -161,16 +161,19 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -784,20 +787,20 @@
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="F4" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>18.2</v>
-      </c>
-      <c r="F4" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="G4" s="12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>17</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>6.8</v>
@@ -805,40 +808,38 @@
       <c r="J4" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="12" t="n">
         <v>18.6</v>
       </c>
-      <c r="L4" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>6.8</v>
+      <c r="L4" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>86.8</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>18.1</v>
+        <v>17</v>
       </c>
       <c r="O4" s="3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q4" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="P4" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q4" s="12" t="n">
+      <c r="R4" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="R4" s="12" t="n">
+      <c r="S4" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="S4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="T4" s="3" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="V4" s="14" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="12" t="inlineStr"/>
       <c r="W4" s="12" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
@@ -857,20 +858,20 @@
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="F5" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="F5" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>10.8</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>16.8</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>5.4</v>
@@ -878,38 +879,40 @@
       <c r="J5" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="K5" s="3" t="n">
-        <v>0.4</v>
+      <c r="K5" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>18.6</v>
+        <v>17.1</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>18.8</v>
+        <v>15.8</v>
       </c>
       <c r="N5" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q5" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="O5" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="12" t="n">
+      <c r="R5" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="R5" s="12" t="n">
+      <c r="S5" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v>21.8</v>
-      </c>
       <c r="T5" s="3" t="n">
-        <v>58</v>
+        <v>54.8</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="12" t="n">
         <v>24.8</v>
       </c>
       <c r="W5" s="12" t="n">
@@ -919,10 +922,10 @@
         <v>17.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>5.6</v>
+        <v>56.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>13.6</v>
+        <v>21.8</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -937,17 +940,19 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="9" t="n">
-        <v>2.8</v>
+      <c r="C6" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>28.6</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>17.8</v>
       </c>
-      <c r="F6" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G6" s="3" t="n">
+      <c r="F6" s="12" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G6" s="12" t="n">
         <v>10.8</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -959,41 +964,41 @@
       <c r="J6" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>16.8</v>
+        <v>18.8</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>86</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" s="12" t="n">
+      <c r="Q6" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R6" s="12" t="n">
+      <c r="R6" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>58</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="V6" s="3" t="n">
-        <v>25.8</v>
+      <c r="V6" s="12" t="n">
+        <v>24.6</v>
       </c>
       <c r="W6" s="12" t="n">
         <v>20</v>
@@ -1005,7 +1010,7 @@
         <v>67</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>10.2</v>
+        <v>656.4</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1020,7 +1025,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D7" s="12" t="n">
         <v>30.4</v>
       </c>
@@ -1040,30 +1047,30 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="K7" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="K7" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="8" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>7.4</v>
+      <c r="L7" s="9" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>17.4</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q7" s="12" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="R7" s="12" t="n">
+      <c r="Q7" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R7" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1073,22 +1080,22 @@
         <v>42.6</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="V7" s="9" t="n">
-        <v>0.4</v>
+        <v>17</v>
+      </c>
+      <c r="V7" s="12" t="n">
+        <v>25.8</v>
       </c>
       <c r="W7" s="12" t="n">
         <v>19.6</v>
       </c>
-      <c r="X7" s="3" t="n">
+      <c r="X7" s="8" t="n">
         <v>19.2</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>14.9</v>
+        <v>14</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1104,31 +1111,35 @@
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E8" s="12" t="inlineStr"/>
-      <c r="F8" s="3" t="n">
-        <v>22.9</v>
+      <c r="D8" s="3" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>53.9</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>15.4</v>
+        <v>19.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.1</v>
+        <v>6.9</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="14" t="inlineStr"/>
+      <c r="L8" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="M8" s="3" t="n">
-        <v>16.4</v>
+        <v>17.4</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>17.4</v>
@@ -1136,34 +1147,38 @@
       <c r="O8" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="12" t="n">
+      <c r="P8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="R8" s="12" t="n">
+      <c r="R8" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>45.9</v>
+        <v>42</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>25.8</v>
+        <v>24.8</v>
+      </c>
+      <c r="V8" s="12" t="n">
+        <v>26.2</v>
       </c>
       <c r="W8" s="12" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="X8" s="8" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z8" s="3" t="n">
         <v>19.4</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="Y8" s="3" t="inlineStr"/>
-      <c r="Z8" s="3" t="n">
-        <v>14.8</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1178,27 +1193,29 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D9" s="10" t="n">
         <v>142.8</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="F9" s="13" t="inlineStr"/>
+      <c r="E9" s="11" t="inlineStr"/>
+      <c r="F9" s="10" t="n">
+        <v>711.7</v>
+      </c>
       <c r="G9" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>27.1</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>34</v>
+        <v>34.8</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="K9" s="10" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="K9" s="12" t="n">
         <v>18.6</v>
       </c>
       <c r="L9" s="10" t="n">
@@ -1208,25 +1225,25 @@
         <v>83.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>423.5</v>
+        <v>201122.1</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Q9" s="10" t="n">
-        <v>192.8</v>
+        <v>142.8</v>
       </c>
       <c r="R9" s="10" t="n">
-        <v>186</v>
+        <v>1196</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>102.6</v>
+        <v>182.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>263.1</v>
+        <v>9255.1</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>99.59999999999999</v>
@@ -1235,16 +1252,16 @@
         <v>127.2</v>
       </c>
       <c r="W9" s="10" t="n">
-        <v>97.40000000000001</v>
+        <v>971.4</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>229.9</v>
+        <v>294.1</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1270,7 +1287,7 @@
         <v>23.4</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>16.5</v>
@@ -1279,10 +1296,10 @@
         <v>6.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>11.3</v>
+        <v>1.1</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>51.1</v>
+        <v>0.1</v>
       </c>
       <c r="L10" s="10" t="n">
         <v>18.8</v>
@@ -1299,35 +1316,35 @@
       <c r="P10" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q10" s="12" t="n">
+      <c r="Q10" s="10" t="n">
         <v>29.2</v>
       </c>
-      <c r="R10" s="12" t="n">
+      <c r="R10" s="10" t="n">
         <v>21.2</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>20.5</v>
+        <v>90.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="V10" s="10" t="n">
+      <c r="V10" s="12" t="n">
         <v>25.4</v>
       </c>
       <c r="W10" s="12" t="n">
         <v>19.5</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>19.1</v>
+        <v>1.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>1141.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>13.9</v>
+        <v>13.4</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1343,23 +1360,23 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="F11" s="3" t="n">
+      <c r="D11" s="12" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F11" s="12" t="n">
         <v>22.6</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>13.2</v>
+        <v>1.5</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>54.6</v>
+        <v>15.4</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>8.199999999999999</v>
@@ -1367,7 +1384,7 @@
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="8" t="n">
+      <c r="L11" s="12" t="n">
         <v>18.4</v>
       </c>
       <c r="M11" s="8" t="n">
@@ -1377,29 +1394,41 @@
         <v>18.9</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>28.9</v>
+        <v>28.4</v>
       </c>
       <c r="R11" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="S11" s="3" t="n">
-        <v>18.4</v>
+      <c r="S11" s="8" t="n">
+        <v>166.6</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="U11" s="3" t="inlineStr"/>
-      <c r="V11" s="12" t="inlineStr"/>
-      <c r="W11" s="12" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr"/>
-      <c r="Y11" s="3" t="inlineStr"/>
-      <c r="Z11" s="3" t="inlineStr"/>
+        <v>13.4</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="W11" s="12" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>13.4</v>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1413,7 +1442,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D12" s="12" t="n">
         <v>28.2</v>
       </c>
@@ -1438,10 +1469,10 @@
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="12" t="n">
         <v>18.6</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1451,7 +1482,7 @@
         <v>89</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="Q12" s="9" t="n">
         <v>2.8</v>
@@ -1463,23 +1494,25 @@
         <v>21.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="U12" s="3" t="inlineStr"/>
-      <c r="V12" s="12" t="n">
-        <v>25.6</v>
+        <v>425.4</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="9" t="n">
+        <v>45.4</v>
       </c>
       <c r="W12" s="12" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>19.7</v>
+        <v>19.4</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>60</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>13.8</v>
+        <v>1.3</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1541,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>6</v>
@@ -1517,9 +1550,9 @@
         <v>9.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" s="12" t="n">
         <v>17.6</v>
       </c>
       <c r="M13" s="3" t="n">
@@ -1529,10 +1562,10 @@
         <v>16.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>23.5</v>
+        <v>83.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>26</v>
@@ -1541,15 +1574,15 @@
         <v>19.9</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>57.1</v>
+        <v>257.1</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V13" s="12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V13" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="W13" s="12" t="n">
@@ -1559,9 +1592,11 @@
         <v>19.7</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>764</v>
-      </c>
-      <c r="Z13" s="3" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>58</v>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1580,35 +1615,37 @@
         <v>27.4</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>19.2</v>
+        <v>20.2</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
+        <v>23.8</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="H14" s="3" t="n">
-        <v>47.8</v>
+        <v>17.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="J14" s="8" t="n">
         <v>11</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="N14" s="8" t="n">
         <v>17.3</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>74.5</v>
+        <v>714.5</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>5.8</v>
@@ -1617,18 +1654,18 @@
         <v>26.8</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>18.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>58</v>
+        <v>51.5</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V14" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="V14" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="W14" s="12" t="n">
@@ -1638,7 +1675,7 @@
         <v>16.8</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>10.6</v>
@@ -1661,12 +1698,12 @@
         <v>28.8</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>17.8</v>
+        <v>18.8</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G15" s="12" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G15" s="3" t="n">
         <v>11</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1678,9 +1715,11 @@
       <c r="J15" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K15" s="14" t="inlineStr"/>
-      <c r="L15" s="3" t="n">
-        <v>11.8</v>
+      <c r="K15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="12" t="n">
+        <v>18.6</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>16.8</v>
@@ -1689,10 +1728,10 @@
         <v>18.1</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>8.4</v>
+        <v>84</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>13.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>28.8</v>
@@ -1709,20 +1748,20 @@
       <c r="U15" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V15" s="12" t="n">
-        <v>25.4</v>
+      <c r="V15" s="3" t="n">
+        <v>23.6</v>
       </c>
       <c r="W15" s="12" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>25</v>
+        <v>18.8</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>114.6</v>
+        <v>18.8</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1737,50 +1776,56 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="10" t="n">
-        <v>1038.8</v>
-      </c>
-      <c r="E16" s="13" t="inlineStr"/>
-      <c r="F16" s="10" t="n">
-        <v>1113.9</v>
-      </c>
-      <c r="G16" s="3" t="n">
+      <c r="C16" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>138.8</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="G16" s="12" t="n">
         <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>3019.1</v>
+        <v>288.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>20.6</v>
+        <v>0.6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>50.6</v>
       </c>
       <c r="K16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>92</v>
       </c>
       <c r="M16" s="10" t="n">
         <v>84</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>914.2</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="P16" s="3" t="inlineStr"/>
+        <v>709.1</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>118.2</v>
+      </c>
       <c r="Q16" s="10" t="n">
-        <v>838.2</v>
-      </c>
-      <c r="R16" s="10" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="R16" s="12" t="n">
         <v>102.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>98.8</v>
+        <v>988.5</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>266.2</v>
@@ -1789,9 +1834,9 @@
         <v>86.2</v>
       </c>
       <c r="V16" s="10" t="n">
-        <v>122.8</v>
-      </c>
-      <c r="W16" s="10" t="n">
+        <v>1943.1</v>
+      </c>
+      <c r="W16" s="12" t="n">
         <v>94.8</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1801,7 +1846,7 @@
         <v>102</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1817,20 +1862,20 @@
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="10" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E17" s="3" t="n">
+      <c r="D17" s="12" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E17" s="12" t="n">
         <v>17.8</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="12" t="n">
         <v>22.8</v>
       </c>
-      <c r="G17" s="8" t="n">
-        <v>0.1</v>
+      <c r="G17" s="12" t="n">
+        <v>10</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>26.8</v>
+        <v>16.8</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>6.1</v>
@@ -1838,51 +1883,53 @@
       <c r="J17" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="10" t="n">
+      <c r="K17" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L17" s="12" t="n">
         <v>18.6</v>
       </c>
       <c r="M17" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>18.1</v>
+        <v>11.8</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>8.4</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" s="10" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="R17" s="12" t="n">
-        <v>20.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="R17" s="10" t="n">
+        <v>11.4</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>13.8</v>
+        <v>19.8</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>52.2</v>
+        <v>51.2</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="V17" s="12" t="n">
+      <c r="V17" s="10" t="n">
         <v>24.6</v>
       </c>
-      <c r="W17" s="12" t="n">
-        <v>19</v>
+      <c r="W17" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>0.1</v>
+        <v>15.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>60.4</v>
+        <v>111.1</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>12.2</v>
+        <v>1.2</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1897,70 +1944,78 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D18" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E18" s="14" t="inlineStr"/>
-      <c r="F18" s="3" t="n">
-        <v>8.4</v>
+        <v>30.4</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>38.4</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1.1</v>
+        <v>13.6</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>13.6</v>
+        <v>456.1</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>13.6</v>
+        <v>126.1</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>18.6</v>
+        <v>0</v>
+      </c>
+      <c r="L18" s="9" t="n">
+        <v>49.6</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>16.2</v>
       </c>
-      <c r="N18" s="3" t="n">
-        <v>17.8</v>
+      <c r="N18" s="8" t="n">
+        <v>68.5</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>78.8</v>
+        <v>810.8</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="Q18" s="3" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="R18" s="8" t="n">
-        <v>29.8</v>
+      <c r="Q18" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R18" s="9" t="n">
+        <v>13.88</v>
       </c>
       <c r="S18" s="3" t="n">
+        <v>904.7</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v>811.1</v>
+      </c>
+      <c r="V18" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="T18" s="3" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="U18" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="V18" s="9" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="W18" s="12" t="n">
-        <v>20.2</v>
+      <c r="W18" s="9" t="n">
+        <v>4.6</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y18" s="3" t="inlineStr"/>
-      <c r="Z18" s="3" t="inlineStr"/>
+        <v>457.1</v>
+      </c>
+      <c r="Y18" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Z18" s="3" t="n">
+        <v>91.40000000000001</v>
+      </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -1975,10 +2030,10 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>17.8</v>
@@ -1990,7 +2045,7 @@
         <v>11.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>6.8</v>
@@ -1999,7 +2054,7 @@
         <v>11.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18.6</v>
@@ -2007,15 +2062,17 @@
       <c r="M19" s="12" t="n">
         <v>17.2</v>
       </c>
-      <c r="N19" s="3" t="n">
-        <v>18.7</v>
+      <c r="N19" s="8" t="n">
+        <v>18.1</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="n">
-        <v>23.6</v>
+        <v>81</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q19" s="9" t="n">
+        <v>92.59999999999999</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>20.8</v>
@@ -2024,7 +2081,7 @@
         <v>19.4</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>96.8</v>
+        <v>46.8</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>22</v>
@@ -2032,17 +2089,17 @@
       <c r="V19" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="W19" s="12" t="n">
+      <c r="W19" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>24</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2057,7 +2114,9 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D20" s="12" t="n">
         <v>30.6</v>
       </c>
@@ -2067,12 +2126,14 @@
       <c r="F20" s="12" t="n">
         <v>24.4</v>
       </c>
-      <c r="G20" s="3" t="inlineStr"/>
+      <c r="G20" s="12" t="n">
+        <v>12.4</v>
+      </c>
       <c r="H20" s="8" t="n">
-        <v>17.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>12.6</v>
@@ -2105,25 +2166,25 @@
         <v>20.9</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W20" s="12" t="n">
+      <c r="W20" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>20</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>58.8</v>
+        <v>58</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>14.4</v>
+        <v>14.9</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2139,14 +2200,14 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>2.2</v>
+      <c r="D21" s="12" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>22.3</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>8.6</v>
@@ -2158,19 +2219,19 @@
         <v>6.6</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>9</v>
+        <v>2.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="9" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>81</v>
@@ -2178,7 +2239,9 @@
       <c r="P21" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q21" s="14" t="inlineStr"/>
+      <c r="Q21" s="3" t="n">
+        <v>26.6</v>
+      </c>
       <c r="R21" s="3" t="n">
         <v>20</v>
       </c>
@@ -2186,22 +2249,22 @@
         <v>19.5</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>256</v>
+        <v>56.8</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="W21" s="12" t="n">
+      <c r="W21" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>12.6</v>
@@ -2219,17 +2282,19 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="3" t="n">
+      <c r="C22" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D22" s="12" t="n">
         <v>28.4</v>
       </c>
-      <c r="E22" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="G22" s="3" t="n">
+      <c r="E22" s="12" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G22" s="12" t="n">
         <v>10.8</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2245,13 +2310,13 @@
         <v>6.8</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>18.2</v>
+        <v>18.9</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>87</v>
@@ -2263,10 +2328,10 @@
         <v>23.2</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>1.9</v>
+        <v>19.5</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>68.3</v>
@@ -2274,20 +2339,20 @@
       <c r="U22" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="V22" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="W22" s="12" t="n">
+      <c r="W22" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>155.1</v>
+        <v>445.4</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>5.7</v>
+        <v>254.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2302,9 +2367,11 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D23" s="10" t="n">
-        <v>19.6</v>
+        <v>1945.6</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>89.40000000000001</v>
@@ -2313,64 +2380,64 @@
         <v>117.8</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>25.2</v>
+        <v>36.2</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>84.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>529.5</v>
+        <v>311.3</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>22.9</v>
+        <v>52.9</v>
       </c>
       <c r="K23" s="10" t="n">
         <v>6.8</v>
       </c>
       <c r="L23" s="10" t="n">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="M23" s="10" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>1426.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>12.8</v>
+        <v>15.6</v>
       </c>
       <c r="Q23" s="10" t="n">
-        <v>44</v>
+        <v>140.4</v>
       </c>
       <c r="R23" s="10" t="n">
-        <v>103.9</v>
+        <v>103.4</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>100.4</v>
+        <v>1108.4</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>8267.799999999999</v>
+        <v>267.8</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>97.59999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="V23" s="10" t="n">
-        <v>123.5</v>
+        <v>1123.5</v>
       </c>
       <c r="W23" s="10" t="n">
-        <v>25.6</v>
+        <v>935.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>94.8</v>
+        <v>26</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>205.4</v>
+        <v>7050.1</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>22.8</v>
+        <v>652.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2399,7 +2466,7 @@
         <v>11.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17</v>
+        <v>17.9</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>6.6</v>
@@ -2407,8 +2474,8 @@
       <c r="J24" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>5.1</v>
+      <c r="K24" s="8" t="n">
+        <v>51.4</v>
       </c>
       <c r="L24" s="10" t="n">
         <v>18.6</v>
@@ -2417,16 +2484,16 @@
         <v>17</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>18.4</v>
+        <v>0.1</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="Q24" s="10" t="n">
-        <v>28.1</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="R24" s="10" t="n">
         <v>20.7</v>
@@ -2435,25 +2502,25 @@
         <v>20.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>53.5</v>
+        <v>0.1</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>18.3</v>
+        <v>1.8</v>
       </c>
       <c r="V24" s="10" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="W24" s="12" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>12.9</v>
+        <v>11.1</v>
+      </c>
+      <c r="W24" s="10" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="X24" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>12.6</v>
+        <v>171.1</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2468,21 +2535,23 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>11.6</v>
+      <c r="C25" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>6.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>10.6</v>
+        <v>1.2</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2</v>
@@ -2494,40 +2563,48 @@
         <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>10.8</v>
+        <v>7.6</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>13.8</v>
+        <v>11.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>16.9</v>
+        <v>16.3</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>83.5</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q25" s="14" t="inlineStr"/>
+        <v>5.4</v>
+      </c>
+      <c r="Q25" s="9" t="n">
+        <v>91.40000000000001</v>
+      </c>
       <c r="R25" s="12" t="n">
         <v>19.4</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>662.3</v>
+        <v>405.5</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>12.8</v>
+        <v>156.1</v>
       </c>
       <c r="U25" s="3" t="inlineStr"/>
       <c r="V25" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="W25" s="12" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="X25" s="3" t="inlineStr"/>
-      <c r="Y25" s="3" t="inlineStr"/>
-      <c r="Z25" s="3" t="inlineStr"/>
+      <c r="W25" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2541,29 +2618,27 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>16</v>
+      <c r="C26" s="3" t="inlineStr"/>
+      <c r="D26" s="12" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>16.8</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.1</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>30.4</v>
@@ -2574,12 +2649,14 @@
       <c r="M26" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>28.8</v>
@@ -2591,25 +2668,25 @@
         <v>20.7</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>12.2</v>
+        <v>52.2</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="V26" s="9" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="W26" s="12" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="W26" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>18.6</v>
+        <v>38.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>19.8</v>
+        <v>112.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2624,50 +2701,48 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>12.8</v>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="12" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>22.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>16.8</v>
+        <v>11</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>68.7</v>
+        <v>6.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>18.1</v>
+        <v>10.6</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M27" s="8" t="n">
+      <c r="M27" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>18.4</v>
+        <v>11.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>22.2</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q27" s="9" t="n">
-        <v>4.1</v>
+      <c r="Q27" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="R27" s="12" t="n">
         <v>20.8</v>
@@ -2676,22 +2751,26 @@
         <v>20.7</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="V27" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W27" s="12" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="V27" s="9" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="W27" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="Y27" s="3" t="inlineStr"/>
-      <c r="Z27" s="3" t="inlineStr"/>
+      <c r="Y27" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2705,42 +2784,44 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G28" s="3" t="n">
+      <c r="C28" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G28" s="12" t="n">
         <v>9.4</v>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>16</v>
+      <c r="H28" s="8" t="n">
+        <v>66</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>7.2</v>
+        <v>8.9</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>18.1</v>
       </c>
       <c r="L28" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>11.6</v>
+        <v>16.6</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>10.7</v>
+        <v>17.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>3.4</v>
@@ -2755,22 +2836,26 @@
         <v>20.7</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>56.7</v>
+        <v>56.9</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="W28" s="12" t="n">
-        <v>19.8</v>
+        <v>29.6</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y28" s="3" t="inlineStr"/>
-      <c r="Z28" s="3" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2784,30 +2869,32 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
+      <c r="C29" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D29" s="12" t="n">
         <v>26.8</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>17.4</v>
+        <v>15.9</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="G29" s="12" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G29" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="H29" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>18.6</v>
@@ -2816,7 +2903,7 @@
         <v>17.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>19.1</v>
+        <v>1.9</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>89</v>
@@ -2831,22 +2918,22 @@
         <v>19.8</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>1.8</v>
+        <v>59.8</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>152.5</v>
+        <v>13.2</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="W29" s="12" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="W29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="X29" s="3" t="n">
-        <v>19.8</v>
+      <c r="X29" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>66.2</v>
@@ -2867,44 +2954,42 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>1334.8</v>
-      </c>
-      <c r="E30" s="10" t="n">
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="12" t="n">
+        <v>133.2</v>
+      </c>
+      <c r="E30" s="12" t="n">
         <v>85.8</v>
       </c>
-      <c r="F30" s="10" t="n">
-        <v>109.8</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>48.4</v>
+      <c r="F30" s="12" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>47.4</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>20</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>32.8</v>
+        <v>39.8</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>90.40000000000001</v>
+        <v>308.4</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>91.40000000000001</v>
+        <v>9434.799999999999</v>
       </c>
       <c r="M30" s="10" t="n">
-        <v>185.4</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>904.6</v>
+        <v>9</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>43464.4</v>
+        <v>428</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>15.2</v>
@@ -2916,28 +3001,28 @@
         <v>102</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>102.2</v>
+        <v>41.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>298.9</v>
+        <v>448.9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="V30" s="10" t="n">
         <v>118.2</v>
       </c>
       <c r="W30" s="10" t="n">
-        <v>99.59999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>418.1</v>
+        <v>44.5</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>3136.2</v>
+        <v>316.2</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>4.6</v>
+        <v>47.6</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2952,9 +3037,7 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="C31" s="3" t="inlineStr"/>
       <c r="D31" s="12" t="n">
         <v>26.6</v>
       </c>
@@ -2964,11 +3047,11 @@
       <c r="F31" s="12" t="n">
         <v>21.9</v>
       </c>
-      <c r="G31" s="3" t="n">
-        <v>9.9</v>
+      <c r="G31" s="12" t="n">
+        <v>9.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>26.1</v>
+        <v>1.6</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>4</v>
@@ -2976,20 +3059,18 @@
       <c r="J31" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>85.2</v>
-      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="10" t="n">
-        <v>18.3</v>
+        <v>10.2</v>
       </c>
       <c r="M31" s="10" t="n">
         <v>16.7</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>18</v>
+        <v>10.1</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>205.1</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>3</v>
@@ -2997,8 +3078,8 @@
       <c r="Q31" s="10" t="n">
         <v>26.4</v>
       </c>
-      <c r="R31" s="12" t="n">
-        <v>20.4</v>
+      <c r="R31" s="10" t="n">
+        <v>10.4</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>20.4</v>
@@ -3007,22 +3088,22 @@
         <v>59.8</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>19.2</v>
+        <v>1.4</v>
       </c>
       <c r="V31" s="10" t="n">
         <v>23.6</v>
       </c>
-      <c r="W31" s="12" t="n">
+      <c r="W31" s="10" t="n">
         <v>19.1</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>475.1</v>
+        <v>17.9</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>10</v>
+        <v>1.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3037,72 +3118,72 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E32" s="14" t="inlineStr"/>
-      <c r="F32" s="3" t="n">
-        <v>21.9</v>
+      <c r="C32" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>19.9</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>15.2</v>
+        <v>0.1</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="L32" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N32" s="3" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="R32" s="12" t="n">
-        <v>19.8</v>
+        <v>4.8</v>
+      </c>
+      <c r="P32" s="3" t="inlineStr"/>
+      <c r="Q32" s="9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>7.4</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="V32" s="12" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="W32" s="12" t="n">
-        <v>18.8</v>
+        <v>96.8</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>198.1</v>
+      </c>
+      <c r="V32" s="12" t="inlineStr"/>
+      <c r="W32" s="9" t="n">
+        <v>44.91</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>19.8</v>
+        <v>4412.8</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr"/>
+        <v>19.5</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>14.6</v>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3117,16 +3198,16 @@
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G33" s="3" t="n">
+      <c r="D33" s="12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="G33" s="12" t="n">
         <v>9.4</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3136,19 +3217,19 @@
         <v>3.3</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="L33" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="M33" s="9" t="n">
-        <v>1.5</v>
+      <c r="M33" s="8" t="n">
+        <v>19.6</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>16.1</v>
+        <v>16.7</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>84</v>
@@ -3157,24 +3238,24 @@
         <v>3.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="R33" s="12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="R33" s="3" t="n">
         <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>19.5</v>
+        <v>19.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>56</v>
+        <v>256</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>15.3</v>
+        <v>1.2</v>
       </c>
       <c r="V33" s="12" t="n">
         <v>21.8</v>
       </c>
-      <c r="W33" s="12" t="n">
+      <c r="W33" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3183,7 +3264,9 @@
       <c r="Y33" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="Z33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="n">
+        <v>5.6</v>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -3198,17 +3281,17 @@
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>1.7</v>
+      <c r="D34" s="9" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>20.9</v>
+        <v>23.1</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>16.6</v>
+        <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>17</v>
@@ -3220,9 +3303,9 @@
         <v>7</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L34" s="12" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="L34" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="M34" s="3" t="n">
@@ -3232,7 +3315,7 @@
         <v>18.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>2</v>
@@ -3240,7 +3323,7 @@
       <c r="Q34" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="R34" s="12" t="n">
+      <c r="R34" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3250,19 +3333,23 @@
         <v>57.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="V34" s="12" t="n">
         <v>24.6</v>
       </c>
-      <c r="W34" s="12" t="n">
+      <c r="W34" s="3" t="n">
         <v>20</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="Y34" s="3" t="inlineStr"/>
-      <c r="Z34" s="3" t="inlineStr"/>
+      <c r="Y34" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>10.8</v>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -3276,20 +3363,18 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D35" s="12" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E35" s="12" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F35" s="12" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="G35" s="12" t="n">
-        <v>10.8</v>
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>6.6</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>16.8</v>
@@ -3303,32 +3388,32 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="12" t="n">
-        <v>17.6</v>
+      <c r="L35" s="8" t="n">
+        <v>17.9</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>19.8</v>
+        <v>15.8</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q35" s="9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R35" s="12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="R35" s="3" t="n">
         <v>19</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>62.2</v>
+        <v>82.2</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>11.4</v>
@@ -3336,14 +3421,18 @@
       <c r="V35" s="12" t="n">
         <v>20.4</v>
       </c>
-      <c r="W35" s="12" t="n">
+      <c r="W35" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="Y35" s="3" t="inlineStr"/>
-      <c r="Z35" s="3" t="inlineStr"/>
+      <c r="Y35" s="3" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3359,13 +3448,13 @@
       </c>
       <c r="C36" s="3" t="inlineStr"/>
       <c r="D36" s="12" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>1.8</v>
+        <v>28.6</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>17.8</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>7.3</v>
+        <v>23.2</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>10.8</v>
@@ -3382,11 +3471,11 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="12" t="n">
-        <v>18.6</v>
+      <c r="L36" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>7.2</v>
+        <v>17.2</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>18.8</v>
@@ -3400,29 +3489,29 @@
       <c r="Q36" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R36" s="12" t="n">
+      <c r="R36" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>26.4</v>
+        <v>56.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>17</v>
+        <v>1.3</v>
       </c>
       <c r="V36" s="12" t="n">
         <v>20.4</v>
       </c>
-      <c r="W36" s="12" t="n">
+      <c r="W36" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>86.5</v>
+        <v>86.8</v>
       </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3438,72 +3527,74 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
+      <c r="C37" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D37" s="10" t="n">
-        <v>1138.8</v>
+        <v>130.8</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>88.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F37" s="10" t="n">
         <v>111</v>
       </c>
-      <c r="G37" s="9" t="n">
-        <v>49.9</v>
+      <c r="G37" s="3" t="n">
+        <v>45.6</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>898</v>
+        <v>87</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>210.9</v>
+        <v>40.9</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>31.8</v>
+        <v>31.5</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L37" s="12" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="L37" s="10" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="M37" s="10" t="n">
-        <v>82.59999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>82.2</v>
+        <v>89.5</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>12.6</v>
+        <v>420.9</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>44.5</v>
+        <v>149.4</v>
       </c>
       <c r="Q37" s="10" t="n">
         <v>132.8</v>
       </c>
-      <c r="R37" s="12" t="n">
-        <v>102.2</v>
+      <c r="R37" s="10" t="n">
+        <v>2.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>10.1</v>
+        <v>101.9</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>208.6</v>
+        <v>120.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="V37" s="12" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="V37" s="10" t="n">
         <v>109.8</v>
       </c>
       <c r="W37" s="10" t="n">
-        <v>18.4</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>10.1</v>
+        <v>101.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>156</v>
+        <v>12.8</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>31.2</v>
@@ -3531,8 +3622,8 @@
       <c r="F38" s="12" t="n">
         <v>22.2</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>92.09999999999999</v>
+      <c r="G38" s="12" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>17</v>
@@ -3541,19 +3632,17 @@
         <v>4.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L38" s="12" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="10" t="n">
         <v>18.1</v>
       </c>
       <c r="M38" s="10" t="n">
         <v>16.5</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>17.9</v>
+        <v>1.8</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>86.09999999999999</v>
@@ -3564,31 +3653,33 @@
       <c r="Q38" s="10" t="n">
         <v>26.8</v>
       </c>
-      <c r="R38" s="12" t="n">
+      <c r="R38" s="10" t="n">
         <v>20.4</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>88.5</v>
+        <v>28.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>57.7</v>
+        <v>5.4</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="V38" s="10" t="n">
-        <v>240.1</v>
-      </c>
-      <c r="W38" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="X38" s="3" t="n">
-        <v>20.3</v>
+      <c r="V38" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="W38" s="10" t="n">
+        <v>12790.1</v>
+      </c>
+      <c r="X38" s="8" t="n">
+        <v>111.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>77.2</v>
-      </c>
-      <c r="Z38" s="3" t="inlineStr"/>
+        <v>1.4</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3602,72 +3693,76 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="12" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E39" s="12" t="n">
+      <c r="C39" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="E39" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="F39" s="12" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G39" s="12" t="n">
-        <v>8</v>
+      <c r="F39" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>4.6</v>
-      </c>
+        <v>16.8</v>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="n">
         <v>8</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L39" s="12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L39" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>19.6</v>
+        <v>19</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>8.4</v>
+        <v>84.8</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R39" s="14" t="inlineStr"/>
-      <c r="S39" s="8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Q39" s="9" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="R39" s="9" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="S39" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="V39" s="12" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="W39" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="V39" s="9" t="n">
+        <v>75.42999999999999</v>
+      </c>
+      <c r="W39" s="12" t="n">
         <v>18.6</v>
       </c>
       <c r="X39" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="Z39" s="3" t="inlineStr"/>
+        <v>64.8</v>
+      </c>
+      <c r="Z39" s="3" t="n">
+        <v>48.8</v>
+      </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -3681,66 +3776,66 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>22.8</v>
+      <c r="C40" s="3" t="inlineStr"/>
+      <c r="D40" s="12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>22.4</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>8.4</v>
+        <v>16.4</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L40" s="12" t="n">
+      <c r="J40" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="L40" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="N40" s="8" t="n">
+      <c r="N40" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>84</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="V40" s="12" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="V40" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="W40" s="3" t="n">
-        <v>18.6</v>
+      <c r="W40" s="12" t="n">
+        <v>18.2</v>
       </c>
       <c r="X40" s="3" t="n">
         <v>20.1</v>
@@ -3763,25 +3858,25 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D41" s="12" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="E41" s="12" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F41" s="12" t="n">
-        <v>22.1</v>
+        <v>11.1</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>2.1</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>17</v>
+        <v>20.1</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>43.5</v>
+        <v>3.5</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>6</v>
@@ -3789,49 +3884,49 @@
       <c r="K41" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="L41" s="12" t="n">
+      <c r="L41" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="M41" s="9" t="n">
-        <v>1.7</v>
+      <c r="M41" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>18.3</v>
+        <v>1.8</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="P41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q41" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.5</v>
+        <v>62.9</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="V41" s="12" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W41" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W41" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>14.4</v>
+        <v>17.2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3846,36 +3941,38 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="3" t="n">
-        <v>30.4</v>
+      <c r="D42" s="9" t="n">
+        <v>48.6</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="F42" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>14</v>
+      <c r="F42" s="8" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>94</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr"/>
+        <v>65.40000000000001</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="12" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="M42" s="3" t="n">
+      <c r="L42" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M42" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>17.8</v>
+        <v>17</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>85</v>
@@ -3886,30 +3983,32 @@
       <c r="Q42" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R42" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="S42" s="3" t="n">
+        <v>20.4</v>
+      </c>
       <c r="T42" s="3" t="n">
         <v>52</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="V42" s="12" t="n">
+      <c r="V42" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="12" t="n">
         <v>20</v>
       </c>
       <c r="X42" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>57</v>
+        <v>1.4</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3926,17 +4025,19 @@
       </c>
       <c r="C43" s="3" t="inlineStr"/>
       <c r="D43" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F43" s="14" t="inlineStr"/>
-      <c r="G43" s="8" t="n">
-        <v>18.5</v>
+        <v>20.4</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>19.2</v>
+        <v>174.4</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>8.6</v>
@@ -3947,50 +4048,50 @@
       <c r="K43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="12" t="n">
+      <c r="L43" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="M43" s="3" t="n">
+      <c r="M43" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>15.9</v>
+        <v>13.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="R43" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="S43" s="3" t="n">
-        <v>18.8</v>
+      <c r="R43" s="9" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="S43" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>92.59999999999999</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="V43" s="12" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="W43" s="3" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="W43" s="12" t="n">
         <v>20</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>57</v>
+        <v>14.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>14.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4006,51 +4107,51 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="D44" s="9" t="n">
-        <v>98</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="F44" s="9" t="n">
-        <v>21.7</v>
+        <v>1.1</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>14.2</v>
+        <v>26.1</v>
       </c>
       <c r="H44" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J44" s="3" t="n">
         <v>15.8</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>1.5</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="12" t="n">
+      <c r="L44" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N44" s="8" t="n">
+      <c r="N44" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>80.8</v>
+        <v>154.8</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="R44" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="R44" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4059,12 +4160,14 @@
       <c r="T44" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="12" t="n">
+      <c r="U44" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V44" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W44" s="3" t="n">
-        <v>30</v>
+      <c r="W44" s="12" t="n">
+        <v>20.6</v>
       </c>
       <c r="X44" s="3" t="n">
         <v>19.6</v>
@@ -4072,7 +4175,9 @@
       <c r="Y44" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="Z44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="n">
+        <v>81.40000000000001</v>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4088,70 +4193,74 @@
       </c>
       <c r="C45" s="3" t="inlineStr"/>
       <c r="D45" s="10" t="n">
-        <v>1.8</v>
+        <v>11.6</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>22.1</v>
+        <v>8504.1</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>830.6</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>62</v>
+        <v>28.1</v>
+      </c>
+      <c r="G45" s="9" t="n">
+        <v>15.9</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>61</v>
+        <v>53.5</v>
       </c>
       <c r="K45" s="10" t="n">
-        <v>9.9</v>
+        <v>61.3</v>
       </c>
       <c r="L45" s="10" t="n">
-        <v>1089.6</v>
+        <v>59.4</v>
       </c>
       <c r="M45" s="10" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="N45" s="3" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="N45" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O45" s="3" t="inlineStr"/>
+      <c r="O45" s="3" t="n">
+        <v>12499</v>
+      </c>
       <c r="P45" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="Q45" s="10" t="n">
-        <v>650.2</v>
+        <v>11651.1</v>
       </c>
       <c r="R45" s="10" t="n">
-        <v>1.3</v>
+        <v>1181.1</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>746.4</v>
+        <v>1113.1</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>217.9</v>
+        <v>517.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>107.1</v>
+        <v>187.1</v>
       </c>
       <c r="V45" s="10" t="n">
-        <v>12.8</v>
+        <v>145.1</v>
       </c>
       <c r="W45" s="10" t="n">
-        <v>114.8</v>
+        <v>111.6</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>1.8</v>
+        <v>392.9</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="Z45" s="3" t="inlineStr"/>
+        <v>69.40000000000001</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>1156.4</v>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4166,17 +4275,17 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="9" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="E46" s="10" t="n">
+      <c r="D46" s="12" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E46" s="12" t="n">
         <v>17.1</v>
       </c>
-      <c r="F46" s="10" t="n">
-        <v>22.8</v>
+      <c r="F46" s="12" t="n">
+        <v>22.5</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10.8</v>
+        <v>19.8</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>15.4</v>
@@ -4187,15 +4296,17 @@
       <c r="J46" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="12" t="n">
+      <c r="K46" s="3" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="L46" s="10" t="n">
         <v>18.3</v>
       </c>
       <c r="M46" s="10" t="n">
         <v>16.4</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>17.2</v>
+        <v>17.8</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>83.09999999999999</v>
@@ -4209,28 +4320,30 @@
       <c r="R46" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="S46" s="3" t="n">
-        <v>19.3</v>
+      <c r="S46" s="8" t="n">
+        <v>19.8</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="V46" s="12" t="n">
+      <c r="V46" s="10" t="n">
         <v>23.8</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="12" t="n">
         <v>19</v>
       </c>
       <c r="X46" s="3" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="Y46" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="Y46" s="3" t="n">
-        <v>165.4</v>
-      </c>
-      <c r="Z46" s="3" t="inlineStr"/>
+      <c r="Z46" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_recheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_recheck_temp_thresholds.xlsx
@@ -1202,7 +1202,7 @@
       <c r="J9" s="3" t="n">
         <v>256.4</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="10" t="n">
         <v>10</v>
       </c>
       <c r="L9" s="3" t="n">
@@ -1775,7 +1775,7 @@
       <c r="J16" s="3" t="n">
         <v>50.6</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="3" t="n">
@@ -2352,7 +2352,7 @@
       <c r="J23" s="3" t="n">
         <v>52.9</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="L23" s="3" t="n">
@@ -2680,7 +2680,7 @@
       <c r="J27" s="3" t="n">
         <v>6.3</v>
       </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="14" t="n"/>
       <c r="L27" s="3" t="n">
         <v>98.8</v>
       </c>
@@ -2925,7 +2925,7 @@
       <c r="J30" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="10" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="L30" s="3" t="n">
@@ -3496,7 +3496,7 @@
       <c r="J37" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="10" t="n">
         <v>18.6</v>
       </c>
       <c r="L37" s="3" t="n">
@@ -4140,7 +4140,7 @@
       <c r="J45" s="3" t="n">
         <v>61.9</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="10" t="n">
         <v>9.4</v>
       </c>
       <c r="L45" s="3" t="n">
